--- a/FreeLayout/Mau_Report_Detail.xlsx
+++ b/FreeLayout/Mau_Report_Detail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\FreeLayout\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SCM Inovation\FreeLayout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DC52FD-AF3B-4681-9DB5-ABE5D77FB43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A8D6E2-8698-4828-B7D0-B19E785E5243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2A4EDF3B-70CC-4D79-8378-AD958291D9C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A4EDF3B-70CC-4D79-8378-AD958291D9C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Report details" sheetId="1" r:id="rId1"/>
@@ -252,7 +252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -338,39 +338,40 @@
     <xf numFmtId="164" fontId="3" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -9450,7 +9451,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" style="36" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" customWidth="1"/>
@@ -9468,7 +9469,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="34" t="s">
         <v>32</v>
       </c>
       <c r="C1" s="6"/>
@@ -9485,7 +9486,7 @@
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="27"/>
       <c r="B2" s="10" t="s">
         <v>33</v>
@@ -9532,107 +9533,107 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="38"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="33"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="38"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="33"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="31"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="42"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="43"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="23"/>
       <c r="L5" s="42"/>
       <c r="M5" s="42"/>
       <c r="N5" s="42"/>
-      <c r="O5" s="40"/>
+      <c r="O5" s="33"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="34"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="21"/>
       <c r="I7" s="42"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="43"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="23"/>
       <c r="L7" s="42"/>
       <c r="M7" s="42"/>
       <c r="N7" s="42"/>
-      <c r="O7" s="40"/>
+      <c r="O7" s="33"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B9" s="25"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -9648,7 +9649,7 @@
       <c r="O9" s="25"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="25"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
@@ -9664,7 +9665,7 @@
       <c r="O10" s="25"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="25"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
@@ -9680,7 +9681,7 @@
       <c r="O11" s="25"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="25"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
@@ -9696,7 +9697,7 @@
       <c r="O12" s="25"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="25"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
@@ -9712,7 +9713,7 @@
       <c r="O13" s="25"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B14" s="25"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="25"/>
       <c r="D14" s="25"/>
       <c r="E14" s="25"/>
@@ -9728,7 +9729,7 @@
       <c r="O14" s="25"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="25"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
@@ -9744,7 +9745,7 @@
       <c r="O15" s="25"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="25"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="25"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
@@ -9760,7 +9761,7 @@
       <c r="O16" s="25"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="25"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="25"/>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -9776,7 +9777,7 @@
       <c r="O17" s="25"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="25"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="25"/>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
@@ -9792,7 +9793,7 @@
       <c r="O18" s="25"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="25"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="25"/>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -9808,7 +9809,7 @@
       <c r="O19" s="25"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="25"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="25"/>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
@@ -9824,7 +9825,7 @@
       <c r="O20" s="25"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="25"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="25"/>
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
@@ -9840,7 +9841,7 @@
       <c r="O21" s="25"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="25"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="25"/>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
@@ -9856,7 +9857,7 @@
       <c r="O22" s="25"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="25"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="25"/>
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
@@ -9872,7 +9873,7 @@
       <c r="O23" s="25"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="25"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="25"/>
       <c r="D24" s="25"/>
       <c r="E24" s="25"/>
@@ -9888,7 +9889,7 @@
       <c r="O24" s="25"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B25" s="25"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
       <c r="E25" s="25"/>
@@ -9904,7 +9905,7 @@
       <c r="O25" s="25"/>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="25"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
       <c r="E26" s="25"/>
@@ -9920,7 +9921,7 @@
       <c r="O26" s="25"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B27" s="25"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="25"/>
       <c r="D27" s="25"/>
       <c r="E27" s="25"/>
@@ -9936,7 +9937,7 @@
       <c r="O27" s="25"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="25"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="25"/>
       <c r="D28" s="25"/>
       <c r="E28" s="25"/>
@@ -9952,7 +9953,7 @@
       <c r="O28" s="25"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="25"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="E29" s="25"/>
@@ -9968,7 +9969,7 @@
       <c r="O29" s="25"/>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="25"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="E30" s="25"/>
@@ -9984,7 +9985,7 @@
       <c r="O30" s="25"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="25"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="E31" s="25"/>
@@ -10000,7 +10001,7 @@
       <c r="O31" s="25"/>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B32" s="25"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
@@ -10016,7 +10017,7 @@
       <c r="O32" s="25"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="25"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="E33" s="25"/>
@@ -10032,7 +10033,7 @@
       <c r="O33" s="25"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="25"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="E34" s="25"/>
@@ -10048,7 +10049,7 @@
       <c r="O34" s="25"/>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="25"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="E35" s="25"/>
@@ -10064,7 +10065,7 @@
       <c r="O35" s="25"/>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B36" s="25"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="E36" s="25"/>
@@ -10080,7 +10081,7 @@
       <c r="O36" s="25"/>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B37" s="25"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="25"/>
       <c r="D37" s="25"/>
       <c r="E37" s="25"/>
@@ -10096,7 +10097,7 @@
       <c r="O37" s="25"/>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="25"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="25"/>
       <c r="D38" s="25"/>
       <c r="E38" s="25"/>
@@ -10112,7 +10113,7 @@
       <c r="O38" s="25"/>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="25"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="25"/>
       <c r="D39" s="25"/>
       <c r="E39" s="25"/>
@@ -10128,7 +10129,7 @@
       <c r="O39" s="25"/>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B40" s="25"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="25"/>
       <c r="D40" s="25"/>
       <c r="E40" s="25"/>
@@ -10144,7 +10145,7 @@
       <c r="O40" s="25"/>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B41" s="25"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="25"/>
       <c r="D41" s="25"/>
       <c r="E41" s="25"/>
@@ -10160,7 +10161,7 @@
       <c r="O41" s="25"/>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B42" s="25"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="25"/>
       <c r="D42" s="25"/>
       <c r="E42" s="25"/>
@@ -10176,7 +10177,7 @@
       <c r="O42" s="25"/>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B43" s="25"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
       <c r="E43" s="25"/>
@@ -10192,7 +10193,7 @@
       <c r="O43" s="25"/>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B44" s="25"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="25"/>
       <c r="D44" s="25"/>
       <c r="E44" s="25"/>
@@ -10208,7 +10209,7 @@
       <c r="O44" s="25"/>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B45" s="25"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="25"/>
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
@@ -10224,7 +10225,7 @@
       <c r="O45" s="25"/>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B46" s="25"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="25"/>
       <c r="D46" s="25"/>
       <c r="E46" s="25"/>
@@ -10240,7 +10241,7 @@
       <c r="O46" s="25"/>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="25"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="25"/>
       <c r="D47" s="25"/>
       <c r="E47" s="25"/>
@@ -10256,7 +10257,7 @@
       <c r="O47" s="25"/>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="25"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="25"/>
       <c r="D48" s="25"/>
       <c r="E48" s="25"/>
@@ -10272,7 +10273,7 @@
       <c r="O48" s="25"/>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B49" s="25"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="25"/>
       <c r="D49" s="25"/>
       <c r="E49" s="25"/>
@@ -10288,7 +10289,7 @@
       <c r="O49" s="25"/>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B50" s="25"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="25"/>
       <c r="D50" s="25"/>
       <c r="E50" s="25"/>
@@ -10304,7 +10305,7 @@
       <c r="O50" s="25"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="25"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="25"/>
       <c r="D51" s="25"/>
       <c r="E51" s="25"/>
@@ -10320,7 +10321,7 @@
       <c r="O51" s="25"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B52" s="25"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="25"/>
       <c r="D52" s="25"/>
       <c r="E52" s="25"/>
@@ -10336,7 +10337,7 @@
       <c r="O52" s="25"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B53" s="25"/>
+      <c r="B53" s="35"/>
       <c r="C53" s="25"/>
       <c r="D53" s="25"/>
       <c r="E53" s="25"/>
@@ -10352,7 +10353,7 @@
       <c r="O53" s="25"/>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B54" s="25"/>
+      <c r="B54" s="35"/>
       <c r="C54" s="25"/>
       <c r="D54" s="25"/>
       <c r="E54" s="25"/>
@@ -10368,7 +10369,7 @@
       <c r="O54" s="25"/>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B55" s="25"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="25"/>
       <c r="D55" s="25"/>
       <c r="E55" s="25"/>
@@ -10384,7 +10385,7 @@
       <c r="O55" s="25"/>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B56" s="25"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="25"/>
       <c r="D56" s="25"/>
       <c r="E56" s="25"/>
@@ -10400,7 +10401,7 @@
       <c r="O56" s="25"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B57" s="25"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="25"/>
       <c r="D57" s="25"/>
       <c r="E57" s="25"/>
@@ -10416,7 +10417,7 @@
       <c r="O57" s="25"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B58" s="25"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="25"/>
       <c r="D58" s="25"/>
       <c r="E58" s="25"/>
@@ -10432,7 +10433,7 @@
       <c r="O58" s="25"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B59" s="25"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="25"/>
       <c r="D59" s="25"/>
       <c r="E59" s="25"/>
@@ -10448,7 +10449,7 @@
       <c r="O59" s="25"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B60" s="25"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="25"/>
       <c r="D60" s="25"/>
       <c r="E60" s="25"/>
@@ -10464,7 +10465,7 @@
       <c r="O60" s="25"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B61" s="25"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="25"/>
       <c r="D61" s="25"/>
       <c r="E61" s="25"/>
@@ -10480,7 +10481,7 @@
       <c r="O61" s="25"/>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B62" s="25"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="25"/>
       <c r="D62" s="25"/>
       <c r="E62" s="25"/>
@@ -10496,7 +10497,7 @@
       <c r="O62" s="25"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B63" s="25"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="25"/>
       <c r="D63" s="25"/>
       <c r="E63" s="25"/>
@@ -10512,7 +10513,7 @@
       <c r="O63" s="25"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B64" s="25"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="25"/>
       <c r="D64" s="25"/>
       <c r="E64" s="25"/>
@@ -10528,7 +10529,7 @@
       <c r="O64" s="25"/>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B65" s="25"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="25"/>
       <c r="D65" s="25"/>
       <c r="E65" s="25"/>
@@ -10544,7 +10545,7 @@
       <c r="O65" s="25"/>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B66" s="25"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="25"/>
       <c r="D66" s="25"/>
       <c r="E66" s="25"/>
@@ -10560,7 +10561,7 @@
       <c r="O66" s="25"/>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B67" s="25"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="25"/>
       <c r="D67" s="25"/>
       <c r="E67" s="25"/>
@@ -10576,7 +10577,7 @@
       <c r="O67" s="25"/>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B68" s="25"/>
+      <c r="B68" s="35"/>
       <c r="C68" s="25"/>
       <c r="D68" s="25"/>
       <c r="E68" s="25"/>
@@ -10592,7 +10593,7 @@
       <c r="O68" s="25"/>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B69" s="25"/>
+      <c r="B69" s="35"/>
       <c r="C69" s="25"/>
       <c r="D69" s="25"/>
       <c r="E69" s="25"/>
@@ -10608,7 +10609,7 @@
       <c r="O69" s="25"/>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B70" s="25"/>
+      <c r="B70" s="35"/>
       <c r="C70" s="25"/>
       <c r="D70" s="25"/>
       <c r="E70" s="25"/>
@@ -10624,7 +10625,7 @@
       <c r="O70" s="25"/>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B71" s="25"/>
+      <c r="B71" s="35"/>
       <c r="C71" s="25"/>
       <c r="D71" s="25"/>
       <c r="E71" s="25"/>
@@ -10640,7 +10641,7 @@
       <c r="O71" s="25"/>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B72" s="25"/>
+      <c r="B72" s="35"/>
       <c r="C72" s="25"/>
       <c r="D72" s="25"/>
       <c r="E72" s="25"/>
@@ -10656,7 +10657,7 @@
       <c r="O72" s="25"/>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B73" s="25"/>
+      <c r="B73" s="35"/>
       <c r="C73" s="25"/>
       <c r="D73" s="25"/>
       <c r="E73" s="25"/>
@@ -10672,7 +10673,7 @@
       <c r="O73" s="25"/>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B74" s="25"/>
+      <c r="B74" s="35"/>
       <c r="C74" s="25"/>
       <c r="D74" s="25"/>
       <c r="E74" s="25"/>
@@ -10688,7 +10689,7 @@
       <c r="O74" s="25"/>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B75" s="25"/>
+      <c r="B75" s="35"/>
       <c r="C75" s="25"/>
       <c r="D75" s="25"/>
       <c r="E75" s="25"/>
@@ -10704,7 +10705,7 @@
       <c r="O75" s="25"/>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B76" s="25"/>
+      <c r="B76" s="35"/>
       <c r="C76" s="25"/>
       <c r="D76" s="25"/>
       <c r="E76" s="25"/>
@@ -10720,7 +10721,7 @@
       <c r="O76" s="25"/>
     </row>
     <row r="77" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B77" s="25"/>
+      <c r="B77" s="35"/>
       <c r="C77" s="25"/>
       <c r="D77" s="25"/>
       <c r="E77" s="25"/>
@@ -10736,7 +10737,7 @@
       <c r="O77" s="25"/>
     </row>
     <row r="78" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B78" s="25"/>
+      <c r="B78" s="35"/>
       <c r="C78" s="25"/>
       <c r="D78" s="25"/>
       <c r="E78" s="25"/>
@@ -10752,7 +10753,7 @@
       <c r="O78" s="25"/>
     </row>
     <row r="79" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B79" s="25"/>
+      <c r="B79" s="35"/>
       <c r="C79" s="25"/>
       <c r="D79" s="25"/>
       <c r="E79" s="25"/>
@@ -10768,7 +10769,7 @@
       <c r="O79" s="25"/>
     </row>
     <row r="80" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B80" s="25"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="25"/>
       <c r="D80" s="25"/>
       <c r="E80" s="25"/>
@@ -10784,7 +10785,7 @@
       <c r="O80" s="25"/>
     </row>
     <row r="81" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B81" s="25"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="25"/>
       <c r="D81" s="25"/>
       <c r="E81" s="25"/>
@@ -10800,7 +10801,7 @@
       <c r="O81" s="25"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B82" s="25"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="25"/>
       <c r="D82" s="25"/>
       <c r="E82" s="25"/>
@@ -10816,7 +10817,7 @@
       <c r="O82" s="25"/>
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B83" s="25"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="25"/>
       <c r="D83" s="25"/>
       <c r="E83" s="25"/>
@@ -10832,7 +10833,7 @@
       <c r="O83" s="25"/>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B84" s="25"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="25"/>
       <c r="D84" s="25"/>
       <c r="E84" s="25"/>
@@ -10848,7 +10849,7 @@
       <c r="O84" s="25"/>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B85" s="25"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="25"/>
       <c r="D85" s="25"/>
       <c r="E85" s="25"/>
@@ -10864,7 +10865,7 @@
       <c r="O85" s="25"/>
     </row>
     <row r="86" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B86" s="25"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="25"/>
       <c r="D86" s="25"/>
       <c r="E86" s="25"/>
@@ -10880,7 +10881,7 @@
       <c r="O86" s="25"/>
     </row>
     <row r="87" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B87" s="25"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="25"/>
       <c r="D87" s="25"/>
       <c r="E87" s="25"/>
@@ -10896,7 +10897,7 @@
       <c r="O87" s="25"/>
     </row>
     <row r="88" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B88" s="25"/>
+      <c r="B88" s="35"/>
       <c r="C88" s="25"/>
       <c r="D88" s="25"/>
       <c r="E88" s="25"/>
@@ -10912,7 +10913,7 @@
       <c r="O88" s="25"/>
     </row>
     <row r="89" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B89" s="25"/>
+      <c r="B89" s="35"/>
       <c r="C89" s="25"/>
       <c r="D89" s="25"/>
       <c r="E89" s="25"/>
@@ -10928,7 +10929,7 @@
       <c r="O89" s="25"/>
     </row>
     <row r="90" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B90" s="25"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="25"/>
       <c r="D90" s="25"/>
       <c r="E90" s="25"/>
@@ -10944,7 +10945,7 @@
       <c r="O90" s="25"/>
     </row>
     <row r="91" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B91" s="25"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="25"/>
       <c r="D91" s="25"/>
       <c r="E91" s="25"/>
@@ -10960,7 +10961,7 @@
       <c r="O91" s="25"/>
     </row>
     <row r="92" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B92" s="25"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="25"/>
       <c r="D92" s="25"/>
       <c r="E92" s="25"/>
@@ -10976,7 +10977,7 @@
       <c r="O92" s="25"/>
     </row>
     <row r="93" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B93" s="25"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="25"/>
       <c r="D93" s="25"/>
       <c r="E93" s="25"/>
@@ -10992,7 +10993,7 @@
       <c r="O93" s="25"/>
     </row>
     <row r="94" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B94" s="25"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="25"/>
       <c r="D94" s="25"/>
       <c r="E94" s="25"/>
@@ -11008,7 +11009,7 @@
       <c r="O94" s="25"/>
     </row>
     <row r="95" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B95" s="25"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="25"/>
       <c r="D95" s="25"/>
       <c r="E95" s="25"/>
@@ -11024,7 +11025,7 @@
       <c r="O95" s="25"/>
     </row>
     <row r="96" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B96" s="25"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="25"/>
       <c r="D96" s="25"/>
       <c r="E96" s="25"/>
@@ -11040,7 +11041,7 @@
       <c r="O96" s="25"/>
     </row>
     <row r="97" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B97" s="25"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="25"/>
       <c r="D97" s="25"/>
       <c r="E97" s="25"/>
@@ -11056,7 +11057,7 @@
       <c r="O97" s="25"/>
     </row>
     <row r="98" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B98" s="25"/>
+      <c r="B98" s="35"/>
       <c r="C98" s="25"/>
       <c r="D98" s="25"/>
       <c r="E98" s="25"/>
@@ -11072,7 +11073,7 @@
       <c r="O98" s="25"/>
     </row>
     <row r="99" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B99" s="25"/>
+      <c r="B99" s="35"/>
       <c r="C99" s="25"/>
       <c r="D99" s="25"/>
       <c r="E99" s="25"/>
@@ -11088,7 +11089,7 @@
       <c r="O99" s="25"/>
     </row>
     <row r="100" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B100" s="25"/>
+      <c r="B100" s="35"/>
       <c r="C100" s="25"/>
       <c r="D100" s="25"/>
       <c r="E100" s="25"/>
@@ -11104,7 +11105,7 @@
       <c r="O100" s="25"/>
     </row>
     <row r="101" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B101" s="25"/>
+      <c r="B101" s="35"/>
       <c r="C101" s="25"/>
       <c r="D101" s="25"/>
       <c r="E101" s="25"/>
@@ -11120,7 +11121,7 @@
       <c r="O101" s="25"/>
     </row>
     <row r="102" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B102" s="25"/>
+      <c r="B102" s="35"/>
       <c r="C102" s="25"/>
       <c r="D102" s="25"/>
       <c r="E102" s="25"/>
@@ -11136,7 +11137,7 @@
       <c r="O102" s="25"/>
     </row>
     <row r="103" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B103" s="25"/>
+      <c r="B103" s="35"/>
       <c r="C103" s="25"/>
       <c r="D103" s="25"/>
       <c r="E103" s="25"/>
@@ -11152,7 +11153,7 @@
       <c r="O103" s="25"/>
     </row>
     <row r="104" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B104" s="25"/>
+      <c r="B104" s="35"/>
       <c r="C104" s="25"/>
       <c r="D104" s="25"/>
       <c r="E104" s="25"/>
@@ -11168,7 +11169,7 @@
       <c r="O104" s="25"/>
     </row>
     <row r="105" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B105" s="25"/>
+      <c r="B105" s="35"/>
       <c r="C105" s="25"/>
       <c r="D105" s="25"/>
       <c r="E105" s="25"/>
@@ -11184,7 +11185,7 @@
       <c r="O105" s="25"/>
     </row>
     <row r="106" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B106" s="25"/>
+      <c r="B106" s="35"/>
       <c r="C106" s="25"/>
       <c r="D106" s="25"/>
       <c r="E106" s="25"/>
@@ -11200,7 +11201,7 @@
       <c r="O106" s="25"/>
     </row>
     <row r="107" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B107" s="25"/>
+      <c r="B107" s="35"/>
       <c r="C107" s="25"/>
       <c r="D107" s="25"/>
       <c r="E107" s="25"/>
@@ -11216,7 +11217,7 @@
       <c r="O107" s="25"/>
     </row>
     <row r="108" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B108" s="25"/>
+      <c r="B108" s="35"/>
       <c r="C108" s="25"/>
       <c r="D108" s="25"/>
       <c r="E108" s="25"/>
@@ -11232,7 +11233,7 @@
       <c r="O108" s="25"/>
     </row>
     <row r="109" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B109" s="25"/>
+      <c r="B109" s="35"/>
       <c r="C109" s="25"/>
       <c r="D109" s="25"/>
       <c r="E109" s="25"/>
@@ -11248,7 +11249,7 @@
       <c r="O109" s="25"/>
     </row>
     <row r="110" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B110" s="25"/>
+      <c r="B110" s="35"/>
       <c r="C110" s="25"/>
       <c r="D110" s="25"/>
       <c r="E110" s="25"/>
@@ -11264,7 +11265,7 @@
       <c r="O110" s="25"/>
     </row>
     <row r="111" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B111" s="25"/>
+      <c r="B111" s="35"/>
       <c r="C111" s="25"/>
       <c r="D111" s="25"/>
       <c r="E111" s="25"/>
@@ -11280,7 +11281,7 @@
       <c r="O111" s="25"/>
     </row>
     <row r="112" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B112" s="25"/>
+      <c r="B112" s="35"/>
       <c r="C112" s="25"/>
       <c r="D112" s="25"/>
       <c r="E112" s="25"/>
@@ -11296,7 +11297,7 @@
       <c r="O112" s="25"/>
     </row>
     <row r="113" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B113" s="25"/>
+      <c r="B113" s="35"/>
       <c r="C113" s="25"/>
       <c r="D113" s="25"/>
       <c r="E113" s="25"/>
@@ -11312,7 +11313,7 @@
       <c r="O113" s="25"/>
     </row>
     <row r="114" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B114" s="25"/>
+      <c r="B114" s="35"/>
       <c r="C114" s="25"/>
       <c r="D114" s="25"/>
       <c r="E114" s="25"/>
@@ -11328,7 +11329,7 @@
       <c r="O114" s="25"/>
     </row>
     <row r="115" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B115" s="25"/>
+      <c r="B115" s="35"/>
       <c r="C115" s="25"/>
       <c r="D115" s="25"/>
       <c r="E115" s="25"/>
@@ -11344,7 +11345,7 @@
       <c r="O115" s="25"/>
     </row>
     <row r="116" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B116" s="25"/>
+      <c r="B116" s="35"/>
       <c r="C116" s="25"/>
       <c r="D116" s="25"/>
       <c r="E116" s="25"/>
@@ -11360,7 +11361,7 @@
       <c r="O116" s="25"/>
     </row>
     <row r="117" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B117" s="25"/>
+      <c r="B117" s="35"/>
       <c r="C117" s="25"/>
       <c r="D117" s="25"/>
       <c r="E117" s="25"/>
@@ -11376,7 +11377,7 @@
       <c r="O117" s="25"/>
     </row>
     <row r="118" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B118" s="25"/>
+      <c r="B118" s="35"/>
       <c r="C118" s="25"/>
       <c r="D118" s="25"/>
       <c r="E118" s="25"/>
@@ -11392,7 +11393,7 @@
       <c r="O118" s="25"/>
     </row>
     <row r="119" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B119" s="25"/>
+      <c r="B119" s="35"/>
       <c r="C119" s="25"/>
       <c r="D119" s="25"/>
       <c r="E119" s="25"/>
@@ -11408,7 +11409,7 @@
       <c r="O119" s="25"/>
     </row>
     <row r="120" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B120" s="25"/>
+      <c r="B120" s="35"/>
       <c r="C120" s="25"/>
       <c r="D120" s="25"/>
       <c r="E120" s="25"/>
@@ -11424,7 +11425,7 @@
       <c r="O120" s="25"/>
     </row>
     <row r="121" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B121" s="25"/>
+      <c r="B121" s="35"/>
       <c r="C121" s="25"/>
       <c r="D121" s="25"/>
       <c r="E121" s="25"/>
@@ -11440,7 +11441,7 @@
       <c r="O121" s="25"/>
     </row>
     <row r="122" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B122" s="25"/>
+      <c r="B122" s="35"/>
       <c r="C122" s="25"/>
       <c r="D122" s="25"/>
       <c r="E122" s="25"/>
@@ -11456,7 +11457,7 @@
       <c r="O122" s="25"/>
     </row>
     <row r="123" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B123" s="25"/>
+      <c r="B123" s="35"/>
       <c r="C123" s="25"/>
       <c r="D123" s="25"/>
       <c r="E123" s="25"/>
@@ -11472,7 +11473,7 @@
       <c r="O123" s="25"/>
     </row>
     <row r="124" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B124" s="25"/>
+      <c r="B124" s="35"/>
       <c r="C124" s="25"/>
       <c r="D124" s="25"/>
       <c r="E124" s="25"/>
@@ -11488,7 +11489,7 @@
       <c r="O124" s="25"/>
     </row>
     <row r="125" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B125" s="25"/>
+      <c r="B125" s="35"/>
       <c r="C125" s="25"/>
       <c r="D125" s="25"/>
       <c r="E125" s="25"/>
@@ -11504,7 +11505,7 @@
       <c r="O125" s="25"/>
     </row>
     <row r="126" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B126" s="25"/>
+      <c r="B126" s="35"/>
       <c r="C126" s="25"/>
       <c r="D126" s="25"/>
       <c r="E126" s="25"/>
@@ -11520,7 +11521,7 @@
       <c r="O126" s="25"/>
     </row>
     <row r="127" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B127" s="25"/>
+      <c r="B127" s="35"/>
       <c r="C127" s="25"/>
       <c r="D127" s="25"/>
       <c r="E127" s="25"/>
@@ -11536,7 +11537,7 @@
       <c r="O127" s="25"/>
     </row>
     <row r="128" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B128" s="25"/>
+      <c r="B128" s="35"/>
       <c r="C128" s="25"/>
       <c r="D128" s="25"/>
       <c r="E128" s="25"/>
@@ -11552,7 +11553,7 @@
       <c r="O128" s="25"/>
     </row>
     <row r="129" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B129" s="25"/>
+      <c r="B129" s="35"/>
       <c r="C129" s="25"/>
       <c r="D129" s="25"/>
       <c r="E129" s="25"/>
@@ -11568,7 +11569,7 @@
       <c r="O129" s="25"/>
     </row>
     <row r="130" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B130" s="25"/>
+      <c r="B130" s="35"/>
       <c r="C130" s="25"/>
       <c r="D130" s="25"/>
       <c r="E130" s="25"/>
@@ -11584,7 +11585,7 @@
       <c r="O130" s="25"/>
     </row>
     <row r="131" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B131" s="25"/>
+      <c r="B131" s="35"/>
       <c r="C131" s="25"/>
       <c r="D131" s="25"/>
       <c r="E131" s="25"/>
@@ -11600,7 +11601,7 @@
       <c r="O131" s="25"/>
     </row>
     <row r="132" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B132" s="25"/>
+      <c r="B132" s="35"/>
       <c r="C132" s="25"/>
       <c r="D132" s="25"/>
       <c r="E132" s="25"/>
@@ -11616,7 +11617,7 @@
       <c r="O132" s="25"/>
     </row>
     <row r="133" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B133" s="25"/>
+      <c r="B133" s="35"/>
       <c r="C133" s="25"/>
       <c r="D133" s="25"/>
       <c r="E133" s="25"/>
@@ -11632,7 +11633,7 @@
       <c r="O133" s="25"/>
     </row>
     <row r="134" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B134" s="25"/>
+      <c r="B134" s="35"/>
       <c r="C134" s="25"/>
       <c r="D134" s="25"/>
       <c r="E134" s="25"/>
@@ -11648,7 +11649,7 @@
       <c r="O134" s="25"/>
     </row>
     <row r="135" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B135" s="25"/>
+      <c r="B135" s="35"/>
       <c r="C135" s="25"/>
       <c r="D135" s="25"/>
       <c r="E135" s="25"/>
@@ -11664,7 +11665,7 @@
       <c r="O135" s="25"/>
     </row>
     <row r="136" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B136" s="25"/>
+      <c r="B136" s="35"/>
       <c r="C136" s="25"/>
       <c r="D136" s="25"/>
       <c r="E136" s="25"/>
@@ -11680,7 +11681,7 @@
       <c r="O136" s="25"/>
     </row>
     <row r="137" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B137" s="25"/>
+      <c r="B137" s="35"/>
       <c r="C137" s="25"/>
       <c r="D137" s="25"/>
       <c r="E137" s="25"/>
@@ -11696,7 +11697,7 @@
       <c r="O137" s="25"/>
     </row>
     <row r="138" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B138" s="25"/>
+      <c r="B138" s="35"/>
       <c r="C138" s="25"/>
       <c r="D138" s="25"/>
       <c r="E138" s="25"/>
@@ -11712,7 +11713,7 @@
       <c r="O138" s="25"/>
     </row>
     <row r="139" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B139" s="25"/>
+      <c r="B139" s="35"/>
       <c r="C139" s="25"/>
       <c r="D139" s="25"/>
       <c r="E139" s="25"/>
@@ -11728,7 +11729,7 @@
       <c r="O139" s="25"/>
     </row>
     <row r="140" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B140" s="25"/>
+      <c r="B140" s="35"/>
       <c r="C140" s="25"/>
       <c r="D140" s="25"/>
       <c r="E140" s="25"/>
@@ -11744,7 +11745,7 @@
       <c r="O140" s="25"/>
     </row>
     <row r="141" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B141" s="25"/>
+      <c r="B141" s="35"/>
       <c r="C141" s="25"/>
       <c r="D141" s="25"/>
       <c r="E141" s="25"/>
@@ -11760,7 +11761,7 @@
       <c r="O141" s="25"/>
     </row>
     <row r="142" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B142" s="25"/>
+      <c r="B142" s="35"/>
       <c r="C142" s="25"/>
       <c r="D142" s="25"/>
       <c r="E142" s="25"/>
@@ -11776,7 +11777,7 @@
       <c r="O142" s="25"/>
     </row>
     <row r="143" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B143" s="25"/>
+      <c r="B143" s="35"/>
       <c r="C143" s="25"/>
       <c r="D143" s="25"/>
       <c r="E143" s="25"/>
@@ -11792,7 +11793,7 @@
       <c r="O143" s="25"/>
     </row>
     <row r="144" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B144" s="25"/>
+      <c r="B144" s="35"/>
       <c r="C144" s="25"/>
       <c r="D144" s="25"/>
       <c r="E144" s="25"/>
@@ -11808,7 +11809,7 @@
       <c r="O144" s="25"/>
     </row>
     <row r="145" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B145" s="25"/>
+      <c r="B145" s="35"/>
       <c r="C145" s="25"/>
       <c r="D145" s="25"/>
       <c r="E145" s="25"/>
@@ -11824,7 +11825,7 @@
       <c r="O145" s="25"/>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B146" s="25"/>
+      <c r="B146" s="35"/>
       <c r="C146" s="25"/>
       <c r="D146" s="25"/>
       <c r="E146" s="25"/>
@@ -11840,7 +11841,7 @@
       <c r="O146" s="25"/>
     </row>
     <row r="147" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B147" s="25"/>
+      <c r="B147" s="35"/>
       <c r="C147" s="25"/>
       <c r="D147" s="25"/>
       <c r="E147" s="25"/>
@@ -11856,7 +11857,7 @@
       <c r="O147" s="25"/>
     </row>
     <row r="148" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B148" s="25"/>
+      <c r="B148" s="35"/>
       <c r="C148" s="25"/>
       <c r="D148" s="25"/>
       <c r="E148" s="25"/>
@@ -11872,7 +11873,7 @@
       <c r="O148" s="25"/>
     </row>
     <row r="149" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B149" s="25"/>
+      <c r="B149" s="35"/>
       <c r="C149" s="25"/>
       <c r="D149" s="25"/>
       <c r="E149" s="25"/>
@@ -11888,7 +11889,7 @@
       <c r="O149" s="25"/>
     </row>
     <row r="150" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B150" s="25"/>
+      <c r="B150" s="35"/>
       <c r="C150" s="25"/>
       <c r="D150" s="25"/>
       <c r="E150" s="25"/>
@@ -11904,7 +11905,7 @@
       <c r="O150" s="25"/>
     </row>
     <row r="151" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B151" s="25"/>
+      <c r="B151" s="35"/>
       <c r="C151" s="25"/>
       <c r="D151" s="25"/>
       <c r="E151" s="25"/>
@@ -11920,7 +11921,7 @@
       <c r="O151" s="25"/>
     </row>
     <row r="152" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B152" s="25"/>
+      <c r="B152" s="35"/>
       <c r="C152" s="25"/>
       <c r="D152" s="25"/>
       <c r="E152" s="25"/>
@@ -11936,7 +11937,7 @@
       <c r="O152" s="25"/>
     </row>
     <row r="153" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B153" s="25"/>
+      <c r="B153" s="35"/>
       <c r="C153" s="25"/>
       <c r="D153" s="25"/>
       <c r="E153" s="25"/>
@@ -11952,7 +11953,7 @@
       <c r="O153" s="25"/>
     </row>
     <row r="154" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B154" s="25"/>
+      <c r="B154" s="35"/>
       <c r="C154" s="25"/>
       <c r="D154" s="25"/>
       <c r="E154" s="25"/>
@@ -11968,7 +11969,7 @@
       <c r="O154" s="25"/>
     </row>
     <row r="155" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B155" s="25"/>
+      <c r="B155" s="35"/>
       <c r="C155" s="25"/>
       <c r="D155" s="25"/>
       <c r="E155" s="25"/>
@@ -11984,7 +11985,7 @@
       <c r="O155" s="25"/>
     </row>
     <row r="156" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B156" s="25"/>
+      <c r="B156" s="35"/>
       <c r="C156" s="25"/>
       <c r="D156" s="25"/>
       <c r="E156" s="25"/>
@@ -12000,7 +12001,7 @@
       <c r="O156" s="25"/>
     </row>
     <row r="157" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B157" s="25"/>
+      <c r="B157" s="35"/>
       <c r="C157" s="25"/>
       <c r="D157" s="25"/>
       <c r="E157" s="25"/>
@@ -12016,7 +12017,7 @@
       <c r="O157" s="25"/>
     </row>
     <row r="158" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B158" s="25"/>
+      <c r="B158" s="35"/>
       <c r="C158" s="25"/>
       <c r="D158" s="25"/>
       <c r="E158" s="25"/>
@@ -12032,7 +12033,7 @@
       <c r="O158" s="25"/>
     </row>
     <row r="159" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B159" s="25"/>
+      <c r="B159" s="35"/>
       <c r="C159" s="25"/>
       <c r="D159" s="25"/>
       <c r="E159" s="25"/>
@@ -12048,7 +12049,7 @@
       <c r="O159" s="25"/>
     </row>
     <row r="160" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B160" s="25"/>
+      <c r="B160" s="35"/>
       <c r="C160" s="25"/>
       <c r="D160" s="25"/>
       <c r="E160" s="25"/>
@@ -12064,7 +12065,7 @@
       <c r="O160" s="25"/>
     </row>
     <row r="161" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B161" s="25"/>
+      <c r="B161" s="35"/>
       <c r="C161" s="25"/>
       <c r="D161" s="25"/>
       <c r="E161" s="25"/>
@@ -12080,7 +12081,7 @@
       <c r="O161" s="25"/>
     </row>
     <row r="162" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B162" s="25"/>
+      <c r="B162" s="35"/>
       <c r="C162" s="25"/>
       <c r="D162" s="25"/>
       <c r="E162" s="25"/>
@@ -12096,7 +12097,7 @@
       <c r="O162" s="25"/>
     </row>
     <row r="163" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B163" s="25"/>
+      <c r="B163" s="35"/>
       <c r="C163" s="25"/>
       <c r="D163" s="25"/>
       <c r="E163" s="25"/>
@@ -12112,7 +12113,7 @@
       <c r="O163" s="25"/>
     </row>
     <row r="164" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B164" s="25"/>
+      <c r="B164" s="35"/>
       <c r="C164" s="25"/>
       <c r="D164" s="25"/>
       <c r="E164" s="25"/>
@@ -12128,7 +12129,7 @@
       <c r="O164" s="25"/>
     </row>
     <row r="165" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B165" s="25"/>
+      <c r="B165" s="35"/>
       <c r="C165" s="25"/>
       <c r="D165" s="25"/>
       <c r="E165" s="25"/>
@@ -12144,7 +12145,7 @@
       <c r="O165" s="25"/>
     </row>
     <row r="166" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B166" s="25"/>
+      <c r="B166" s="35"/>
       <c r="C166" s="25"/>
       <c r="D166" s="25"/>
       <c r="E166" s="25"/>
@@ -12160,7 +12161,7 @@
       <c r="O166" s="25"/>
     </row>
     <row r="167" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B167" s="25"/>
+      <c r="B167" s="35"/>
       <c r="C167" s="25"/>
       <c r="D167" s="25"/>
       <c r="E167" s="25"/>
@@ -12176,7 +12177,7 @@
       <c r="O167" s="25"/>
     </row>
     <row r="168" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B168" s="25"/>
+      <c r="B168" s="35"/>
       <c r="C168" s="25"/>
       <c r="D168" s="25"/>
       <c r="E168" s="25"/>
@@ -12192,7 +12193,7 @@
       <c r="O168" s="25"/>
     </row>
     <row r="169" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B169" s="25"/>
+      <c r="B169" s="35"/>
       <c r="C169" s="25"/>
       <c r="D169" s="25"/>
       <c r="E169" s="25"/>
@@ -12208,7 +12209,7 @@
       <c r="O169" s="25"/>
     </row>
     <row r="170" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B170" s="25"/>
+      <c r="B170" s="35"/>
       <c r="C170" s="25"/>
       <c r="D170" s="25"/>
       <c r="E170" s="25"/>
@@ -12224,7 +12225,7 @@
       <c r="O170" s="25"/>
     </row>
     <row r="171" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B171" s="25"/>
+      <c r="B171" s="35"/>
       <c r="C171" s="25"/>
       <c r="D171" s="25"/>
       <c r="E171" s="25"/>
@@ -12240,7 +12241,7 @@
       <c r="O171" s="25"/>
     </row>
     <row r="172" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B172" s="25"/>
+      <c r="B172" s="35"/>
       <c r="C172" s="25"/>
       <c r="D172" s="25"/>
       <c r="E172" s="25"/>
@@ -12256,7 +12257,7 @@
       <c r="O172" s="25"/>
     </row>
     <row r="173" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B173" s="25"/>
+      <c r="B173" s="35"/>
       <c r="C173" s="25"/>
       <c r="D173" s="25"/>
       <c r="E173" s="25"/>
@@ -12272,7 +12273,7 @@
       <c r="O173" s="25"/>
     </row>
     <row r="174" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B174" s="25"/>
+      <c r="B174" s="35"/>
       <c r="C174" s="25"/>
       <c r="D174" s="25"/>
       <c r="E174" s="25"/>
@@ -12288,7 +12289,7 @@
       <c r="O174" s="25"/>
     </row>
     <row r="175" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B175" s="25"/>
+      <c r="B175" s="35"/>
       <c r="C175" s="25"/>
       <c r="D175" s="25"/>
       <c r="E175" s="25"/>
@@ -12304,7 +12305,7 @@
       <c r="O175" s="25"/>
     </row>
     <row r="176" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B176" s="25"/>
+      <c r="B176" s="35"/>
       <c r="C176" s="25"/>
       <c r="D176" s="25"/>
       <c r="E176" s="25"/>
@@ -12320,7 +12321,7 @@
       <c r="O176" s="25"/>
     </row>
     <row r="177" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B177" s="25"/>
+      <c r="B177" s="35"/>
       <c r="C177" s="25"/>
       <c r="D177" s="25"/>
       <c r="E177" s="25"/>
@@ -12336,7 +12337,7 @@
       <c r="O177" s="25"/>
     </row>
     <row r="178" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B178" s="25"/>
+      <c r="B178" s="35"/>
       <c r="C178" s="25"/>
       <c r="D178" s="25"/>
       <c r="E178" s="25"/>
@@ -12352,7 +12353,7 @@
       <c r="O178" s="25"/>
     </row>
     <row r="179" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B179" s="25"/>
+      <c r="B179" s="35"/>
       <c r="C179" s="25"/>
       <c r="D179" s="25"/>
       <c r="E179" s="25"/>
@@ -12368,7 +12369,7 @@
       <c r="O179" s="25"/>
     </row>
     <row r="180" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B180" s="25"/>
+      <c r="B180" s="35"/>
       <c r="C180" s="25"/>
       <c r="D180" s="25"/>
       <c r="E180" s="25"/>
@@ -12384,7 +12385,7 @@
       <c r="O180" s="25"/>
     </row>
     <row r="181" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B181" s="25"/>
+      <c r="B181" s="35"/>
       <c r="C181" s="25"/>
       <c r="D181" s="25"/>
       <c r="E181" s="25"/>
@@ -12400,7 +12401,7 @@
       <c r="O181" s="25"/>
     </row>
     <row r="182" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B182" s="25"/>
+      <c r="B182" s="35"/>
       <c r="C182" s="25"/>
       <c r="D182" s="25"/>
       <c r="E182" s="25"/>
@@ -12416,7 +12417,7 @@
       <c r="O182" s="25"/>
     </row>
     <row r="183" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B183" s="25"/>
+      <c r="B183" s="35"/>
       <c r="C183" s="25"/>
       <c r="D183" s="25"/>
       <c r="E183" s="25"/>
@@ -12432,7 +12433,7 @@
       <c r="O183" s="25"/>
     </row>
     <row r="184" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B184" s="25"/>
+      <c r="B184" s="35"/>
       <c r="C184" s="25"/>
       <c r="D184" s="25"/>
       <c r="E184" s="25"/>
@@ -12448,7 +12449,7 @@
       <c r="O184" s="25"/>
     </row>
     <row r="185" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B185" s="25"/>
+      <c r="B185" s="35"/>
       <c r="C185" s="25"/>
       <c r="D185" s="25"/>
       <c r="E185" s="25"/>
@@ -12464,7 +12465,7 @@
       <c r="O185" s="25"/>
     </row>
     <row r="186" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B186" s="25"/>
+      <c r="B186" s="35"/>
       <c r="C186" s="25"/>
       <c r="D186" s="25"/>
       <c r="E186" s="25"/>
@@ -12480,7 +12481,7 @@
       <c r="O186" s="25"/>
     </row>
     <row r="187" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B187" s="25"/>
+      <c r="B187" s="35"/>
       <c r="C187" s="25"/>
       <c r="D187" s="25"/>
       <c r="E187" s="25"/>
@@ -12496,7 +12497,7 @@
       <c r="O187" s="25"/>
     </row>
     <row r="188" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B188" s="25"/>
+      <c r="B188" s="35"/>
       <c r="C188" s="25"/>
       <c r="D188" s="25"/>
       <c r="E188" s="25"/>
@@ -12512,7 +12513,7 @@
       <c r="O188" s="25"/>
     </row>
     <row r="189" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B189" s="25"/>
+      <c r="B189" s="35"/>
       <c r="C189" s="25"/>
       <c r="D189" s="25"/>
       <c r="E189" s="25"/>
@@ -12528,7 +12529,7 @@
       <c r="O189" s="25"/>
     </row>
     <row r="190" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B190" s="25"/>
+      <c r="B190" s="35"/>
       <c r="C190" s="25"/>
       <c r="D190" s="25"/>
       <c r="E190" s="25"/>
@@ -12544,7 +12545,7 @@
       <c r="O190" s="25"/>
     </row>
     <row r="191" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B191" s="25"/>
+      <c r="B191" s="35"/>
       <c r="C191" s="25"/>
       <c r="D191" s="25"/>
       <c r="E191" s="25"/>
@@ -12560,7 +12561,7 @@
       <c r="O191" s="25"/>
     </row>
     <row r="192" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B192" s="25"/>
+      <c r="B192" s="35"/>
       <c r="C192" s="25"/>
       <c r="D192" s="25"/>
       <c r="E192" s="25"/>
@@ -12576,7 +12577,7 @@
       <c r="O192" s="25"/>
     </row>
     <row r="193" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B193" s="25"/>
+      <c r="B193" s="35"/>
       <c r="C193" s="25"/>
       <c r="D193" s="25"/>
       <c r="E193" s="25"/>
@@ -12592,7 +12593,7 @@
       <c r="O193" s="25"/>
     </row>
     <row r="194" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B194" s="25"/>
+      <c r="B194" s="35"/>
       <c r="C194" s="25"/>
       <c r="D194" s="25"/>
       <c r="E194" s="25"/>
@@ -12608,7 +12609,7 @@
       <c r="O194" s="25"/>
     </row>
     <row r="195" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B195" s="25"/>
+      <c r="B195" s="35"/>
       <c r="C195" s="25"/>
       <c r="D195" s="25"/>
       <c r="E195" s="25"/>
@@ -12624,7 +12625,7 @@
       <c r="O195" s="25"/>
     </row>
     <row r="196" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B196" s="25"/>
+      <c r="B196" s="35"/>
       <c r="C196" s="25"/>
       <c r="D196" s="25"/>
       <c r="E196" s="25"/>
@@ -12640,7 +12641,7 @@
       <c r="O196" s="25"/>
     </row>
     <row r="197" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B197" s="25"/>
+      <c r="B197" s="35"/>
       <c r="C197" s="25"/>
       <c r="D197" s="25"/>
       <c r="E197" s="25"/>
@@ -12656,7 +12657,7 @@
       <c r="O197" s="25"/>
     </row>
     <row r="198" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B198" s="25"/>
+      <c r="B198" s="35"/>
       <c r="C198" s="25"/>
       <c r="D198" s="25"/>
       <c r="E198" s="25"/>
@@ -12672,7 +12673,7 @@
       <c r="O198" s="25"/>
     </row>
     <row r="199" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B199" s="25"/>
+      <c r="B199" s="35"/>
       <c r="C199" s="25"/>
       <c r="D199" s="25"/>
       <c r="E199" s="25"/>
@@ -12688,7 +12689,7 @@
       <c r="O199" s="25"/>
     </row>
     <row r="200" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B200" s="25"/>
+      <c r="B200" s="35"/>
       <c r="C200" s="25"/>
       <c r="D200" s="25"/>
       <c r="E200" s="25"/>
@@ -12704,7 +12705,7 @@
       <c r="O200" s="25"/>
     </row>
     <row r="201" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B201" s="25"/>
+      <c r="B201" s="35"/>
       <c r="C201" s="25"/>
       <c r="D201" s="25"/>
       <c r="E201" s="25"/>
@@ -12720,7 +12721,7 @@
       <c r="O201" s="25"/>
     </row>
     <row r="202" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B202" s="25"/>
+      <c r="B202" s="35"/>
       <c r="C202" s="25"/>
       <c r="D202" s="25"/>
       <c r="E202" s="25"/>
@@ -12736,7 +12737,7 @@
       <c r="O202" s="25"/>
     </row>
     <row r="203" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B203" s="25"/>
+      <c r="B203" s="35"/>
       <c r="C203" s="25"/>
       <c r="D203" s="25"/>
       <c r="E203" s="25"/>
@@ -12752,7 +12753,7 @@
       <c r="O203" s="25"/>
     </row>
     <row r="204" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B204" s="25"/>
+      <c r="B204" s="35"/>
       <c r="C204" s="25"/>
       <c r="D204" s="25"/>
       <c r="E204" s="25"/>
@@ -12768,7 +12769,7 @@
       <c r="O204" s="25"/>
     </row>
     <row r="205" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B205" s="25"/>
+      <c r="B205" s="35"/>
       <c r="C205" s="25"/>
       <c r="D205" s="25"/>
       <c r="E205" s="25"/>
@@ -12784,7 +12785,7 @@
       <c r="O205" s="25"/>
     </row>
     <row r="206" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B206" s="25"/>
+      <c r="B206" s="35"/>
       <c r="C206" s="25"/>
       <c r="D206" s="25"/>
       <c r="E206" s="25"/>
@@ -12800,7 +12801,7 @@
       <c r="O206" s="25"/>
     </row>
     <row r="207" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B207" s="25"/>
+      <c r="B207" s="35"/>
       <c r="C207" s="25"/>
       <c r="D207" s="25"/>
       <c r="E207" s="25"/>
@@ -12816,7 +12817,7 @@
       <c r="O207" s="25"/>
     </row>
     <row r="208" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B208" s="25"/>
+      <c r="B208" s="35"/>
       <c r="C208" s="25"/>
       <c r="D208" s="25"/>
       <c r="E208" s="25"/>
@@ -12832,7 +12833,7 @@
       <c r="O208" s="25"/>
     </row>
     <row r="209" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B209" s="25"/>
+      <c r="B209" s="35"/>
       <c r="C209" s="25"/>
       <c r="D209" s="25"/>
       <c r="E209" s="25"/>
@@ -12848,7 +12849,7 @@
       <c r="O209" s="25"/>
     </row>
     <row r="210" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B210" s="25"/>
+      <c r="B210" s="35"/>
       <c r="C210" s="25"/>
       <c r="D210" s="25"/>
       <c r="E210" s="25"/>
@@ -12864,7 +12865,7 @@
       <c r="O210" s="25"/>
     </row>
     <row r="211" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B211" s="25"/>
+      <c r="B211" s="35"/>
       <c r="C211" s="25"/>
       <c r="D211" s="25"/>
       <c r="E211" s="25"/>
@@ -12880,7 +12881,7 @@
       <c r="O211" s="25"/>
     </row>
     <row r="212" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B212" s="25"/>
+      <c r="B212" s="35"/>
       <c r="C212" s="25"/>
       <c r="D212" s="25"/>
       <c r="E212" s="25"/>
@@ -12896,7 +12897,7 @@
       <c r="O212" s="25"/>
     </row>
     <row r="213" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B213" s="25"/>
+      <c r="B213" s="35"/>
       <c r="C213" s="25"/>
       <c r="D213" s="25"/>
       <c r="E213" s="25"/>
@@ -12912,7 +12913,7 @@
       <c r="O213" s="25"/>
     </row>
     <row r="214" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B214" s="25"/>
+      <c r="B214" s="35"/>
       <c r="C214" s="25"/>
       <c r="D214" s="25"/>
       <c r="E214" s="25"/>
@@ -12928,7 +12929,7 @@
       <c r="O214" s="25"/>
     </row>
     <row r="215" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B215" s="25"/>
+      <c r="B215" s="35"/>
       <c r="C215" s="25"/>
       <c r="D215" s="25"/>
       <c r="E215" s="25"/>
@@ -12944,7 +12945,7 @@
       <c r="O215" s="25"/>
     </row>
     <row r="216" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B216" s="25"/>
+      <c r="B216" s="35"/>
       <c r="C216" s="25"/>
       <c r="D216" s="25"/>
       <c r="E216" s="25"/>
@@ -12960,7 +12961,7 @@
       <c r="O216" s="25"/>
     </row>
     <row r="217" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B217" s="25"/>
+      <c r="B217" s="35"/>
       <c r="C217" s="25"/>
       <c r="D217" s="25"/>
       <c r="E217" s="25"/>
@@ -12976,7 +12977,7 @@
       <c r="O217" s="25"/>
     </row>
     <row r="218" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B218" s="25"/>
+      <c r="B218" s="35"/>
       <c r="C218" s="25"/>
       <c r="D218" s="25"/>
       <c r="E218" s="25"/>
@@ -12992,7 +12993,7 @@
       <c r="O218" s="25"/>
     </row>
     <row r="219" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B219" s="25"/>
+      <c r="B219" s="35"/>
       <c r="C219" s="25"/>
       <c r="D219" s="25"/>
       <c r="E219" s="25"/>
@@ -13008,7 +13009,7 @@
       <c r="O219" s="25"/>
     </row>
     <row r="220" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B220" s="25"/>
+      <c r="B220" s="35"/>
       <c r="C220" s="25"/>
       <c r="D220" s="25"/>
       <c r="E220" s="25"/>
@@ -13024,7 +13025,7 @@
       <c r="O220" s="25"/>
     </row>
     <row r="221" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B221" s="25"/>
+      <c r="B221" s="35"/>
       <c r="C221" s="25"/>
       <c r="D221" s="25"/>
       <c r="E221" s="25"/>
@@ -13040,7 +13041,7 @@
       <c r="O221" s="25"/>
     </row>
     <row r="222" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B222" s="25"/>
+      <c r="B222" s="35"/>
       <c r="C222" s="25"/>
       <c r="D222" s="25"/>
       <c r="E222" s="25"/>
@@ -13056,7 +13057,7 @@
       <c r="O222" s="25"/>
     </row>
     <row r="223" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B223" s="25"/>
+      <c r="B223" s="35"/>
       <c r="C223" s="25"/>
       <c r="D223" s="25"/>
       <c r="E223" s="25"/>
@@ -13072,7 +13073,7 @@
       <c r="O223" s="25"/>
     </row>
     <row r="224" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B224" s="25"/>
+      <c r="B224" s="35"/>
       <c r="C224" s="25"/>
       <c r="D224" s="25"/>
       <c r="E224" s="25"/>
@@ -13088,7 +13089,7 @@
       <c r="O224" s="25"/>
     </row>
     <row r="225" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B225" s="25"/>
+      <c r="B225" s="35"/>
       <c r="C225" s="25"/>
       <c r="D225" s="25"/>
       <c r="E225" s="25"/>
@@ -13104,7 +13105,7 @@
       <c r="O225" s="25"/>
     </row>
     <row r="226" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B226" s="25"/>
+      <c r="B226" s="35"/>
       <c r="C226" s="25"/>
       <c r="D226" s="25"/>
       <c r="E226" s="25"/>
@@ -13120,7 +13121,7 @@
       <c r="O226" s="25"/>
     </row>
     <row r="227" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B227" s="25"/>
+      <c r="B227" s="35"/>
       <c r="C227" s="25"/>
       <c r="D227" s="25"/>
       <c r="E227" s="25"/>
@@ -13136,7 +13137,7 @@
       <c r="O227" s="25"/>
     </row>
     <row r="228" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B228" s="25"/>
+      <c r="B228" s="35"/>
       <c r="C228" s="25"/>
       <c r="D228" s="25"/>
       <c r="E228" s="25"/>
@@ -13152,7 +13153,7 @@
       <c r="O228" s="25"/>
     </row>
     <row r="229" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B229" s="25"/>
+      <c r="B229" s="35"/>
       <c r="C229" s="25"/>
       <c r="D229" s="25"/>
       <c r="E229" s="25"/>
@@ -13168,7 +13169,7 @@
       <c r="O229" s="25"/>
     </row>
     <row r="230" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B230" s="25"/>
+      <c r="B230" s="35"/>
       <c r="C230" s="25"/>
       <c r="D230" s="25"/>
       <c r="E230" s="25"/>
@@ -13184,7 +13185,7 @@
       <c r="O230" s="25"/>
     </row>
     <row r="231" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B231" s="25"/>
+      <c r="B231" s="35"/>
       <c r="C231" s="25"/>
       <c r="D231" s="25"/>
       <c r="E231" s="25"/>
@@ -13200,7 +13201,7 @@
       <c r="O231" s="25"/>
     </row>
     <row r="232" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B232" s="25"/>
+      <c r="B232" s="35"/>
       <c r="C232" s="25"/>
       <c r="D232" s="25"/>
       <c r="E232" s="25"/>
@@ -13216,7 +13217,7 @@
       <c r="O232" s="25"/>
     </row>
     <row r="233" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B233" s="25"/>
+      <c r="B233" s="35"/>
       <c r="C233" s="25"/>
       <c r="D233" s="25"/>
       <c r="E233" s="25"/>
@@ -13232,7 +13233,7 @@
       <c r="O233" s="25"/>
     </row>
     <row r="234" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B234" s="25"/>
+      <c r="B234" s="35"/>
       <c r="C234" s="25"/>
       <c r="D234" s="25"/>
       <c r="E234" s="25"/>
@@ -13248,7 +13249,7 @@
       <c r="O234" s="25"/>
     </row>
     <row r="235" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B235" s="25"/>
+      <c r="B235" s="35"/>
       <c r="C235" s="25"/>
       <c r="D235" s="25"/>
       <c r="E235" s="25"/>
@@ -13264,7 +13265,7 @@
       <c r="O235" s="25"/>
     </row>
     <row r="236" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B236" s="25"/>
+      <c r="B236" s="35"/>
       <c r="C236" s="25"/>
       <c r="D236" s="25"/>
       <c r="E236" s="25"/>
@@ -13280,7 +13281,7 @@
       <c r="O236" s="25"/>
     </row>
     <row r="237" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B237" s="25"/>
+      <c r="B237" s="35"/>
       <c r="C237" s="25"/>
       <c r="D237" s="25"/>
       <c r="E237" s="25"/>
@@ -13296,7 +13297,7 @@
       <c r="O237" s="25"/>
     </row>
     <row r="238" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B238" s="25"/>
+      <c r="B238" s="35"/>
       <c r="C238" s="25"/>
       <c r="D238" s="25"/>
       <c r="E238" s="25"/>
@@ -13312,7 +13313,7 @@
       <c r="O238" s="25"/>
     </row>
     <row r="239" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B239" s="25"/>
+      <c r="B239" s="35"/>
       <c r="C239" s="25"/>
       <c r="D239" s="25"/>
       <c r="E239" s="25"/>
@@ -13328,7 +13329,7 @@
       <c r="O239" s="25"/>
     </row>
     <row r="240" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B240" s="25"/>
+      <c r="B240" s="35"/>
       <c r="C240" s="25"/>
       <c r="D240" s="25"/>
       <c r="E240" s="25"/>
@@ -13344,7 +13345,7 @@
       <c r="O240" s="25"/>
     </row>
     <row r="241" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B241" s="25"/>
+      <c r="B241" s="35"/>
       <c r="C241" s="25"/>
       <c r="D241" s="25"/>
       <c r="E241" s="25"/>
@@ -13360,7 +13361,7 @@
       <c r="O241" s="25"/>
     </row>
     <row r="242" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B242" s="25"/>
+      <c r="B242" s="35"/>
       <c r="C242" s="25"/>
       <c r="D242" s="25"/>
       <c r="E242" s="25"/>
@@ -13376,7 +13377,7 @@
       <c r="O242" s="25"/>
     </row>
     <row r="243" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B243" s="25"/>
+      <c r="B243" s="35"/>
       <c r="C243" s="25"/>
       <c r="D243" s="25"/>
       <c r="E243" s="25"/>
@@ -13392,7 +13393,7 @@
       <c r="O243" s="25"/>
     </row>
     <row r="244" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B244" s="25"/>
+      <c r="B244" s="35"/>
       <c r="C244" s="25"/>
       <c r="D244" s="25"/>
       <c r="E244" s="25"/>
@@ -13408,7 +13409,7 @@
       <c r="O244" s="25"/>
     </row>
     <row r="245" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B245" s="25"/>
+      <c r="B245" s="35"/>
       <c r="C245" s="25"/>
       <c r="D245" s="25"/>
       <c r="E245" s="25"/>
@@ -13424,7 +13425,7 @@
       <c r="O245" s="25"/>
     </row>
     <row r="246" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B246" s="25"/>
+      <c r="B246" s="35"/>
       <c r="C246" s="25"/>
       <c r="D246" s="25"/>
       <c r="E246" s="25"/>
@@ -13440,7 +13441,7 @@
       <c r="O246" s="25"/>
     </row>
     <row r="247" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B247" s="25"/>
+      <c r="B247" s="35"/>
       <c r="C247" s="25"/>
       <c r="D247" s="25"/>
       <c r="E247" s="25"/>
@@ -13456,7 +13457,7 @@
       <c r="O247" s="25"/>
     </row>
     <row r="248" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B248" s="25"/>
+      <c r="B248" s="35"/>
       <c r="C248" s="25"/>
       <c r="D248" s="25"/>
       <c r="E248" s="25"/>
@@ -13472,7 +13473,7 @@
       <c r="O248" s="25"/>
     </row>
     <row r="249" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B249" s="25"/>
+      <c r="B249" s="35"/>
       <c r="C249" s="25"/>
       <c r="D249" s="25"/>
       <c r="E249" s="25"/>
@@ -13488,7 +13489,7 @@
       <c r="O249" s="25"/>
     </row>
     <row r="250" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B250" s="25"/>
+      <c r="B250" s="35"/>
       <c r="C250" s="25"/>
       <c r="D250" s="25"/>
       <c r="E250" s="25"/>
@@ -13504,7 +13505,7 @@
       <c r="O250" s="25"/>
     </row>
     <row r="251" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B251" s="25"/>
+      <c r="B251" s="35"/>
       <c r="C251" s="25"/>
       <c r="D251" s="25"/>
       <c r="E251" s="25"/>
@@ -13520,7 +13521,7 @@
       <c r="O251" s="25"/>
     </row>
     <row r="252" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B252" s="25"/>
+      <c r="B252" s="35"/>
       <c r="C252" s="25"/>
       <c r="D252" s="25"/>
       <c r="E252" s="25"/>
@@ -13536,7 +13537,7 @@
       <c r="O252" s="25"/>
     </row>
     <row r="253" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B253" s="25"/>
+      <c r="B253" s="35"/>
       <c r="C253" s="25"/>
       <c r="D253" s="25"/>
       <c r="E253" s="25"/>
@@ -13552,7 +13553,7 @@
       <c r="O253" s="25"/>
     </row>
     <row r="254" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B254" s="25"/>
+      <c r="B254" s="35"/>
       <c r="C254" s="25"/>
       <c r="D254" s="25"/>
       <c r="E254" s="25"/>
@@ -13568,7 +13569,7 @@
       <c r="O254" s="25"/>
     </row>
     <row r="255" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B255" s="25"/>
+      <c r="B255" s="35"/>
       <c r="C255" s="25"/>
       <c r="D255" s="25"/>
       <c r="E255" s="25"/>
@@ -13584,7 +13585,7 @@
       <c r="O255" s="25"/>
     </row>
     <row r="256" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B256" s="25"/>
+      <c r="B256" s="35"/>
       <c r="C256" s="25"/>
       <c r="D256" s="25"/>
       <c r="E256" s="25"/>
@@ -13600,7 +13601,7 @@
       <c r="O256" s="25"/>
     </row>
     <row r="257" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B257" s="25"/>
+      <c r="B257" s="35"/>
       <c r="C257" s="25"/>
       <c r="D257" s="25"/>
       <c r="E257" s="25"/>
@@ -13616,7 +13617,7 @@
       <c r="O257" s="25"/>
     </row>
     <row r="258" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B258" s="25"/>
+      <c r="B258" s="35"/>
       <c r="C258" s="25"/>
       <c r="D258" s="25"/>
       <c r="E258" s="25"/>
@@ -13632,7 +13633,7 @@
       <c r="O258" s="25"/>
     </row>
     <row r="259" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B259" s="25"/>
+      <c r="B259" s="35"/>
       <c r="C259" s="25"/>
       <c r="D259" s="25"/>
       <c r="E259" s="25"/>
@@ -13648,7 +13649,7 @@
       <c r="O259" s="25"/>
     </row>
     <row r="260" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B260" s="25"/>
+      <c r="B260" s="35"/>
       <c r="C260" s="25"/>
       <c r="D260" s="25"/>
       <c r="E260" s="25"/>
@@ -13664,7 +13665,7 @@
       <c r="O260" s="25"/>
     </row>
     <row r="261" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B261" s="25"/>
+      <c r="B261" s="35"/>
       <c r="C261" s="25"/>
       <c r="D261" s="25"/>
       <c r="E261" s="25"/>
@@ -13680,7 +13681,7 @@
       <c r="O261" s="25"/>
     </row>
     <row r="262" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B262" s="25"/>
+      <c r="B262" s="35"/>
       <c r="C262" s="25"/>
       <c r="D262" s="25"/>
       <c r="E262" s="25"/>
@@ -13696,7 +13697,7 @@
       <c r="O262" s="25"/>
     </row>
     <row r="263" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B263" s="25"/>
+      <c r="B263" s="35"/>
       <c r="C263" s="25"/>
       <c r="D263" s="25"/>
       <c r="E263" s="25"/>
@@ -13712,7 +13713,7 @@
       <c r="O263" s="25"/>
     </row>
     <row r="264" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B264" s="25"/>
+      <c r="B264" s="35"/>
       <c r="C264" s="25"/>
       <c r="D264" s="25"/>
       <c r="E264" s="25"/>
@@ -13728,7 +13729,7 @@
       <c r="O264" s="25"/>
     </row>
     <row r="265" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B265" s="25"/>
+      <c r="B265" s="35"/>
       <c r="C265" s="25"/>
       <c r="D265" s="25"/>
       <c r="E265" s="25"/>
@@ -13744,7 +13745,7 @@
       <c r="O265" s="25"/>
     </row>
     <row r="266" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B266" s="25"/>
+      <c r="B266" s="35"/>
       <c r="C266" s="25"/>
       <c r="D266" s="25"/>
       <c r="E266" s="25"/>
@@ -13760,7 +13761,7 @@
       <c r="O266" s="25"/>
     </row>
     <row r="267" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B267" s="25"/>
+      <c r="B267" s="35"/>
       <c r="C267" s="25"/>
       <c r="D267" s="25"/>
       <c r="E267" s="25"/>
@@ -13776,7 +13777,7 @@
       <c r="O267" s="25"/>
     </row>
     <row r="268" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B268" s="25"/>
+      <c r="B268" s="35"/>
       <c r="C268" s="25"/>
       <c r="D268" s="25"/>
       <c r="E268" s="25"/>
@@ -13792,7 +13793,7 @@
       <c r="O268" s="25"/>
     </row>
     <row r="269" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B269" s="25"/>
+      <c r="B269" s="35"/>
       <c r="C269" s="25"/>
       <c r="D269" s="25"/>
       <c r="E269" s="25"/>
@@ -13808,7 +13809,7 @@
       <c r="O269" s="25"/>
     </row>
     <row r="270" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B270" s="25"/>
+      <c r="B270" s="35"/>
       <c r="C270" s="25"/>
       <c r="D270" s="25"/>
       <c r="E270" s="25"/>
@@ -13824,7 +13825,7 @@
       <c r="O270" s="25"/>
     </row>
     <row r="271" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B271" s="25"/>
+      <c r="B271" s="35"/>
       <c r="C271" s="25"/>
       <c r="D271" s="25"/>
       <c r="E271" s="25"/>
@@ -13840,7 +13841,7 @@
       <c r="O271" s="25"/>
     </row>
     <row r="272" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B272" s="25"/>
+      <c r="B272" s="35"/>
       <c r="C272" s="25"/>
       <c r="D272" s="25"/>
       <c r="E272" s="25"/>
@@ -13856,7 +13857,7 @@
       <c r="O272" s="25"/>
     </row>
     <row r="273" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B273" s="25"/>
+      <c r="B273" s="35"/>
       <c r="C273" s="25"/>
       <c r="D273" s="25"/>
       <c r="E273" s="25"/>
@@ -13872,7 +13873,7 @@
       <c r="O273" s="25"/>
     </row>
     <row r="274" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B274" s="25"/>
+      <c r="B274" s="35"/>
       <c r="C274" s="25"/>
       <c r="D274" s="25"/>
       <c r="E274" s="25"/>
@@ -13888,7 +13889,7 @@
       <c r="O274" s="25"/>
     </row>
     <row r="275" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B275" s="25"/>
+      <c r="B275" s="35"/>
       <c r="C275" s="25"/>
       <c r="D275" s="25"/>
       <c r="E275" s="25"/>
@@ -13904,7 +13905,7 @@
       <c r="O275" s="25"/>
     </row>
     <row r="276" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B276" s="25"/>
+      <c r="B276" s="35"/>
       <c r="C276" s="25"/>
       <c r="D276" s="25"/>
       <c r="E276" s="25"/>
@@ -13920,7 +13921,7 @@
       <c r="O276" s="25"/>
     </row>
     <row r="277" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B277" s="25"/>
+      <c r="B277" s="35"/>
       <c r="C277" s="25"/>
       <c r="D277" s="25"/>
       <c r="E277" s="25"/>
@@ -13936,7 +13937,7 @@
       <c r="O277" s="25"/>
     </row>
     <row r="278" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B278" s="25"/>
+      <c r="B278" s="35"/>
       <c r="C278" s="25"/>
       <c r="D278" s="25"/>
       <c r="E278" s="25"/>
@@ -13952,7 +13953,7 @@
       <c r="O278" s="25"/>
     </row>
     <row r="279" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B279" s="25"/>
+      <c r="B279" s="35"/>
       <c r="C279" s="25"/>
       <c r="D279" s="25"/>
       <c r="E279" s="25"/>
@@ -13968,7 +13969,7 @@
       <c r="O279" s="25"/>
     </row>
     <row r="280" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B280" s="25"/>
+      <c r="B280" s="35"/>
       <c r="C280" s="25"/>
       <c r="D280" s="25"/>
       <c r="E280" s="25"/>
@@ -13984,7 +13985,7 @@
       <c r="O280" s="25"/>
     </row>
     <row r="281" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B281" s="25"/>
+      <c r="B281" s="35"/>
       <c r="C281" s="25"/>
       <c r="D281" s="25"/>
       <c r="E281" s="25"/>
@@ -14000,7 +14001,7 @@
       <c r="O281" s="25"/>
     </row>
     <row r="282" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B282" s="25"/>
+      <c r="B282" s="35"/>
       <c r="C282" s="25"/>
       <c r="D282" s="25"/>
       <c r="E282" s="25"/>
@@ -14016,7 +14017,7 @@
       <c r="O282" s="25"/>
     </row>
     <row r="283" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B283" s="25"/>
+      <c r="B283" s="35"/>
       <c r="C283" s="25"/>
       <c r="D283" s="25"/>
       <c r="E283" s="25"/>
@@ -14032,7 +14033,7 @@
       <c r="O283" s="25"/>
     </row>
     <row r="284" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B284" s="25"/>
+      <c r="B284" s="35"/>
       <c r="C284" s="25"/>
       <c r="D284" s="25"/>
       <c r="E284" s="25"/>
@@ -14048,7 +14049,7 @@
       <c r="O284" s="25"/>
     </row>
     <row r="285" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B285" s="25"/>
+      <c r="B285" s="35"/>
       <c r="C285" s="25"/>
       <c r="D285" s="25"/>
       <c r="E285" s="25"/>
@@ -14064,7 +14065,7 @@
       <c r="O285" s="25"/>
     </row>
     <row r="286" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B286" s="25"/>
+      <c r="B286" s="35"/>
       <c r="C286" s="25"/>
       <c r="D286" s="25"/>
       <c r="E286" s="25"/>
@@ -14080,7 +14081,7 @@
       <c r="O286" s="25"/>
     </row>
     <row r="287" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B287" s="25"/>
+      <c r="B287" s="35"/>
       <c r="C287" s="25"/>
       <c r="D287" s="25"/>
       <c r="E287" s="25"/>
@@ -14096,7 +14097,7 @@
       <c r="O287" s="25"/>
     </row>
     <row r="288" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B288" s="25"/>
+      <c r="B288" s="35"/>
       <c r="C288" s="25"/>
       <c r="D288" s="25"/>
       <c r="E288" s="25"/>
@@ -14112,7 +14113,7 @@
       <c r="O288" s="25"/>
     </row>
     <row r="289" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B289" s="25"/>
+      <c r="B289" s="35"/>
       <c r="C289" s="25"/>
       <c r="D289" s="25"/>
       <c r="E289" s="25"/>
@@ -14128,7 +14129,7 @@
       <c r="O289" s="25"/>
     </row>
     <row r="290" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B290" s="25"/>
+      <c r="B290" s="35"/>
       <c r="C290" s="25"/>
       <c r="D290" s="25"/>
       <c r="E290" s="25"/>
@@ -14144,7 +14145,7 @@
       <c r="O290" s="25"/>
     </row>
     <row r="291" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B291" s="25"/>
+      <c r="B291" s="35"/>
       <c r="C291" s="25"/>
       <c r="D291" s="25"/>
       <c r="E291" s="25"/>
@@ -14160,7 +14161,7 @@
       <c r="O291" s="25"/>
     </row>
     <row r="292" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B292" s="25"/>
+      <c r="B292" s="35"/>
       <c r="C292" s="25"/>
       <c r="D292" s="25"/>
       <c r="E292" s="25"/>
@@ -14176,7 +14177,7 @@
       <c r="O292" s="25"/>
     </row>
     <row r="293" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B293" s="25"/>
+      <c r="B293" s="35"/>
       <c r="C293" s="25"/>
       <c r="D293" s="25"/>
       <c r="E293" s="25"/>
@@ -14192,7 +14193,7 @@
       <c r="O293" s="25"/>
     </row>
     <row r="294" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B294" s="25"/>
+      <c r="B294" s="35"/>
       <c r="C294" s="25"/>
       <c r="D294" s="25"/>
       <c r="E294" s="25"/>
@@ -14208,7 +14209,7 @@
       <c r="O294" s="25"/>
     </row>
     <row r="295" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B295" s="25"/>
+      <c r="B295" s="35"/>
       <c r="C295" s="25"/>
       <c r="D295" s="25"/>
       <c r="E295" s="25"/>
@@ -14224,7 +14225,7 @@
       <c r="O295" s="25"/>
     </row>
     <row r="296" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B296" s="25"/>
+      <c r="B296" s="35"/>
       <c r="C296" s="25"/>
       <c r="D296" s="25"/>
       <c r="E296" s="25"/>
@@ -14240,7 +14241,7 @@
       <c r="O296" s="25"/>
     </row>
     <row r="297" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B297" s="25"/>
+      <c r="B297" s="35"/>
       <c r="C297" s="25"/>
       <c r="D297" s="25"/>
       <c r="E297" s="25"/>
@@ -14256,7 +14257,7 @@
       <c r="O297" s="25"/>
     </row>
     <row r="298" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B298" s="25"/>
+      <c r="B298" s="35"/>
       <c r="C298" s="25"/>
       <c r="D298" s="25"/>
       <c r="E298" s="25"/>
@@ -14272,7 +14273,7 @@
       <c r="O298" s="25"/>
     </row>
     <row r="299" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B299" s="25"/>
+      <c r="B299" s="35"/>
       <c r="C299" s="25"/>
       <c r="D299" s="25"/>
       <c r="E299" s="25"/>
@@ -14288,7 +14289,7 @@
       <c r="O299" s="25"/>
     </row>
     <row r="300" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B300" s="25"/>
+      <c r="B300" s="35"/>
       <c r="C300" s="25"/>
       <c r="D300" s="25"/>
       <c r="E300" s="25"/>
@@ -14304,7 +14305,7 @@
       <c r="O300" s="25"/>
     </row>
     <row r="301" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B301" s="25"/>
+      <c r="B301" s="35"/>
       <c r="C301" s="25"/>
       <c r="D301" s="25"/>
       <c r="E301" s="25"/>
@@ -14320,7 +14321,7 @@
       <c r="O301" s="25"/>
     </row>
     <row r="302" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B302" s="25"/>
+      <c r="B302" s="35"/>
       <c r="C302" s="25"/>
       <c r="D302" s="25"/>
       <c r="E302" s="25"/>
@@ -14336,7 +14337,7 @@
       <c r="O302" s="25"/>
     </row>
     <row r="303" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B303" s="25"/>
+      <c r="B303" s="35"/>
       <c r="C303" s="25"/>
       <c r="D303" s="25"/>
       <c r="E303" s="25"/>
@@ -14352,7 +14353,7 @@
       <c r="O303" s="25"/>
     </row>
     <row r="304" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B304" s="25"/>
+      <c r="B304" s="35"/>
       <c r="C304" s="25"/>
       <c r="D304" s="25"/>
       <c r="E304" s="25"/>
@@ -14368,7 +14369,7 @@
       <c r="O304" s="25"/>
     </row>
     <row r="305" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B305" s="25"/>
+      <c r="B305" s="35"/>
       <c r="C305" s="25"/>
       <c r="D305" s="25"/>
       <c r="E305" s="25"/>
@@ -14384,7 +14385,7 @@
       <c r="O305" s="25"/>
     </row>
     <row r="306" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B306" s="25"/>
+      <c r="B306" s="35"/>
       <c r="C306" s="25"/>
       <c r="D306" s="25"/>
       <c r="E306" s="25"/>
@@ -14400,7 +14401,7 @@
       <c r="O306" s="25"/>
     </row>
     <row r="307" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B307" s="25"/>
+      <c r="B307" s="35"/>
       <c r="C307" s="25"/>
       <c r="D307" s="25"/>
       <c r="E307" s="25"/>
@@ -14416,7 +14417,7 @@
       <c r="O307" s="25"/>
     </row>
     <row r="308" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B308" s="25"/>
+      <c r="B308" s="35"/>
       <c r="C308" s="25"/>
       <c r="D308" s="25"/>
       <c r="E308" s="25"/>
@@ -14432,7 +14433,7 @@
       <c r="O308" s="25"/>
     </row>
     <row r="309" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B309" s="25"/>
+      <c r="B309" s="35"/>
       <c r="C309" s="25"/>
       <c r="D309" s="25"/>
       <c r="E309" s="25"/>
@@ -14448,7 +14449,7 @@
       <c r="O309" s="25"/>
     </row>
     <row r="310" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B310" s="25"/>
+      <c r="B310" s="35"/>
       <c r="C310" s="25"/>
       <c r="D310" s="25"/>
       <c r="E310" s="25"/>
@@ -14464,7 +14465,7 @@
       <c r="O310" s="25"/>
     </row>
     <row r="311" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B311" s="25"/>
+      <c r="B311" s="35"/>
       <c r="C311" s="25"/>
       <c r="D311" s="25"/>
       <c r="E311" s="25"/>
@@ -14480,7 +14481,7 @@
       <c r="O311" s="25"/>
     </row>
     <row r="312" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B312" s="25"/>
+      <c r="B312" s="35"/>
       <c r="C312" s="25"/>
       <c r="D312" s="25"/>
       <c r="E312" s="25"/>
@@ -14496,7 +14497,7 @@
       <c r="O312" s="25"/>
     </row>
     <row r="313" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B313" s="25"/>
+      <c r="B313" s="35"/>
       <c r="C313" s="25"/>
       <c r="D313" s="25"/>
       <c r="E313" s="25"/>
@@ -14512,7 +14513,7 @@
       <c r="O313" s="25"/>
     </row>
     <row r="314" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B314" s="25"/>
+      <c r="B314" s="35"/>
       <c r="C314" s="25"/>
       <c r="D314" s="25"/>
       <c r="E314" s="25"/>
@@ -14528,7 +14529,7 @@
       <c r="O314" s="25"/>
     </row>
     <row r="315" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B315" s="25"/>
+      <c r="B315" s="35"/>
       <c r="C315" s="25"/>
       <c r="D315" s="25"/>
       <c r="E315" s="25"/>
@@ -14544,7 +14545,7 @@
       <c r="O315" s="25"/>
     </row>
     <row r="316" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B316" s="25"/>
+      <c r="B316" s="35"/>
       <c r="C316" s="25"/>
       <c r="D316" s="25"/>
       <c r="E316" s="25"/>
@@ -14560,7 +14561,7 @@
       <c r="O316" s="25"/>
     </row>
     <row r="317" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B317" s="25"/>
+      <c r="B317" s="35"/>
       <c r="C317" s="25"/>
       <c r="D317" s="25"/>
       <c r="E317" s="25"/>
@@ -14576,7 +14577,7 @@
       <c r="O317" s="25"/>
     </row>
     <row r="318" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B318" s="25"/>
+      <c r="B318" s="35"/>
       <c r="C318" s="25"/>
       <c r="D318" s="25"/>
       <c r="E318" s="25"/>
@@ -14592,7 +14593,7 @@
       <c r="O318" s="25"/>
     </row>
     <row r="319" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B319" s="25"/>
+      <c r="B319" s="35"/>
       <c r="C319" s="25"/>
       <c r="D319" s="25"/>
       <c r="E319" s="25"/>
@@ -14608,7 +14609,7 @@
       <c r="O319" s="25"/>
     </row>
     <row r="320" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B320" s="25"/>
+      <c r="B320" s="35"/>
       <c r="C320" s="25"/>
       <c r="D320" s="25"/>
       <c r="E320" s="25"/>
@@ -14624,7 +14625,7 @@
       <c r="O320" s="25"/>
     </row>
     <row r="321" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B321" s="25"/>
+      <c r="B321" s="35"/>
       <c r="C321" s="25"/>
       <c r="D321" s="25"/>
       <c r="E321" s="25"/>
@@ -14640,7 +14641,7 @@
       <c r="O321" s="25"/>
     </row>
     <row r="322" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B322" s="25"/>
+      <c r="B322" s="35"/>
       <c r="C322" s="25"/>
       <c r="D322" s="25"/>
       <c r="E322" s="25"/>
@@ -14656,7 +14657,7 @@
       <c r="O322" s="25"/>
     </row>
     <row r="323" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B323" s="25"/>
+      <c r="B323" s="35"/>
       <c r="C323" s="25"/>
       <c r="D323" s="25"/>
       <c r="E323" s="25"/>
@@ -14672,7 +14673,7 @@
       <c r="O323" s="25"/>
     </row>
     <row r="324" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B324" s="25"/>
+      <c r="B324" s="35"/>
       <c r="C324" s="25"/>
       <c r="D324" s="25"/>
       <c r="E324" s="25"/>
@@ -14688,7 +14689,7 @@
       <c r="O324" s="25"/>
     </row>
     <row r="325" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B325" s="25"/>
+      <c r="B325" s="35"/>
       <c r="C325" s="25"/>
       <c r="D325" s="25"/>
       <c r="E325" s="25"/>
@@ -14704,7 +14705,7 @@
       <c r="O325" s="25"/>
     </row>
     <row r="326" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B326" s="25"/>
+      <c r="B326" s="35"/>
       <c r="C326" s="25"/>
       <c r="D326" s="25"/>
       <c r="E326" s="25"/>
@@ -14720,7 +14721,7 @@
       <c r="O326" s="25"/>
     </row>
     <row r="327" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B327" s="25"/>
+      <c r="B327" s="35"/>
       <c r="C327" s="25"/>
       <c r="D327" s="25"/>
       <c r="E327" s="25"/>
@@ -14736,7 +14737,7 @@
       <c r="O327" s="25"/>
     </row>
     <row r="328" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B328" s="25"/>
+      <c r="B328" s="35"/>
       <c r="C328" s="25"/>
       <c r="D328" s="25"/>
       <c r="E328" s="25"/>
@@ -14752,7 +14753,7 @@
       <c r="O328" s="25"/>
     </row>
     <row r="329" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B329" s="25"/>
+      <c r="B329" s="35"/>
       <c r="C329" s="25"/>
       <c r="D329" s="25"/>
       <c r="E329" s="25"/>
@@ -14768,7 +14769,7 @@
       <c r="O329" s="25"/>
     </row>
     <row r="330" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B330" s="25"/>
+      <c r="B330" s="35"/>
       <c r="C330" s="25"/>
       <c r="D330" s="25"/>
       <c r="E330" s="25"/>
@@ -14784,7 +14785,7 @@
       <c r="O330" s="25"/>
     </row>
     <row r="331" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B331" s="25"/>
+      <c r="B331" s="35"/>
       <c r="C331" s="25"/>
       <c r="D331" s="25"/>
       <c r="E331" s="25"/>
@@ -14800,7 +14801,7 @@
       <c r="O331" s="25"/>
     </row>
     <row r="332" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B332" s="25"/>
+      <c r="B332" s="35"/>
       <c r="C332" s="25"/>
       <c r="D332" s="25"/>
       <c r="E332" s="25"/>
@@ -14816,7 +14817,7 @@
       <c r="O332" s="25"/>
     </row>
     <row r="333" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B333" s="25"/>
+      <c r="B333" s="35"/>
       <c r="C333" s="25"/>
       <c r="D333" s="25"/>
       <c r="E333" s="25"/>
@@ -14832,7 +14833,7 @@
       <c r="O333" s="25"/>
     </row>
     <row r="334" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B334" s="25"/>
+      <c r="B334" s="35"/>
       <c r="C334" s="25"/>
       <c r="D334" s="25"/>
       <c r="E334" s="25"/>
@@ -14848,7 +14849,7 @@
       <c r="O334" s="25"/>
     </row>
     <row r="335" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B335" s="25"/>
+      <c r="B335" s="35"/>
       <c r="C335" s="25"/>
       <c r="D335" s="25"/>
       <c r="E335" s="25"/>
@@ -14864,7 +14865,7 @@
       <c r="O335" s="25"/>
     </row>
     <row r="336" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B336" s="25"/>
+      <c r="B336" s="35"/>
       <c r="C336" s="25"/>
       <c r="D336" s="25"/>
       <c r="E336" s="25"/>
@@ -14880,7 +14881,7 @@
       <c r="O336" s="25"/>
     </row>
     <row r="337" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B337" s="25"/>
+      <c r="B337" s="35"/>
       <c r="C337" s="25"/>
       <c r="D337" s="25"/>
       <c r="E337" s="25"/>
@@ -14896,7 +14897,7 @@
       <c r="O337" s="25"/>
     </row>
     <row r="338" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B338" s="25"/>
+      <c r="B338" s="35"/>
       <c r="C338" s="25"/>
       <c r="D338" s="25"/>
       <c r="E338" s="25"/>
@@ -14912,7 +14913,7 @@
       <c r="O338" s="25"/>
     </row>
     <row r="339" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B339" s="25"/>
+      <c r="B339" s="35"/>
       <c r="C339" s="25"/>
       <c r="D339" s="25"/>
       <c r="E339" s="25"/>
@@ -14928,7 +14929,7 @@
       <c r="O339" s="25"/>
     </row>
     <row r="340" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B340" s="25"/>
+      <c r="B340" s="35"/>
       <c r="C340" s="25"/>
       <c r="D340" s="25"/>
       <c r="E340" s="25"/>
@@ -14944,7 +14945,7 @@
       <c r="O340" s="25"/>
     </row>
     <row r="341" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B341" s="25"/>
+      <c r="B341" s="35"/>
       <c r="C341" s="25"/>
       <c r="D341" s="25"/>
       <c r="E341" s="25"/>
@@ -14960,7 +14961,7 @@
       <c r="O341" s="25"/>
     </row>
     <row r="342" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B342" s="25"/>
+      <c r="B342" s="35"/>
       <c r="C342" s="25"/>
       <c r="D342" s="25"/>
       <c r="E342" s="25"/>
@@ -14976,7 +14977,7 @@
       <c r="O342" s="25"/>
     </row>
     <row r="343" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B343" s="25"/>
+      <c r="B343" s="35"/>
       <c r="C343" s="25"/>
       <c r="D343" s="25"/>
       <c r="E343" s="25"/>
@@ -14992,7 +14993,7 @@
       <c r="O343" s="25"/>
     </row>
     <row r="344" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B344" s="25"/>
+      <c r="B344" s="35"/>
       <c r="C344" s="25"/>
       <c r="D344" s="25"/>
       <c r="E344" s="25"/>
@@ -15008,7 +15009,7 @@
       <c r="O344" s="25"/>
     </row>
     <row r="345" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B345" s="25"/>
+      <c r="B345" s="35"/>
       <c r="C345" s="25"/>
       <c r="D345" s="25"/>
       <c r="E345" s="25"/>
@@ -15024,7 +15025,7 @@
       <c r="O345" s="25"/>
     </row>
     <row r="346" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B346" s="25"/>
+      <c r="B346" s="35"/>
       <c r="C346" s="25"/>
       <c r="D346" s="25"/>
       <c r="E346" s="25"/>
@@ -15040,7 +15041,7 @@
       <c r="O346" s="25"/>
     </row>
     <row r="347" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B347" s="25"/>
+      <c r="B347" s="35"/>
       <c r="C347" s="25"/>
       <c r="D347" s="25"/>
       <c r="E347" s="25"/>
@@ -15056,7 +15057,7 @@
       <c r="O347" s="25"/>
     </row>
     <row r="348" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B348" s="25"/>
+      <c r="B348" s="35"/>
       <c r="C348" s="25"/>
       <c r="D348" s="25"/>
       <c r="E348" s="25"/>
@@ -15072,7 +15073,7 @@
       <c r="O348" s="25"/>
     </row>
     <row r="349" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B349" s="25"/>
+      <c r="B349" s="35"/>
       <c r="C349" s="25"/>
       <c r="D349" s="25"/>
       <c r="E349" s="25"/>
@@ -15088,7 +15089,7 @@
       <c r="O349" s="25"/>
     </row>
     <row r="350" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B350" s="25"/>
+      <c r="B350" s="35"/>
       <c r="C350" s="25"/>
       <c r="D350" s="25"/>
       <c r="E350" s="25"/>
@@ -15104,7 +15105,7 @@
       <c r="O350" s="25"/>
     </row>
     <row r="351" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B351" s="25"/>
+      <c r="B351" s="35"/>
       <c r="C351" s="25"/>
       <c r="D351" s="25"/>
       <c r="E351" s="25"/>
@@ -15120,7 +15121,7 @@
       <c r="O351" s="25"/>
     </row>
     <row r="352" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B352" s="25"/>
+      <c r="B352" s="35"/>
       <c r="C352" s="25"/>
       <c r="D352" s="25"/>
       <c r="E352" s="25"/>
@@ -15136,7 +15137,7 @@
       <c r="O352" s="25"/>
     </row>
     <row r="353" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B353" s="25"/>
+      <c r="B353" s="35"/>
       <c r="C353" s="25"/>
       <c r="D353" s="25"/>
       <c r="E353" s="25"/>
@@ -15152,7 +15153,7 @@
       <c r="O353" s="25"/>
     </row>
     <row r="354" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B354" s="25"/>
+      <c r="B354" s="35"/>
       <c r="C354" s="25"/>
       <c r="D354" s="25"/>
       <c r="E354" s="25"/>
@@ -15168,7 +15169,7 @@
       <c r="O354" s="25"/>
     </row>
     <row r="355" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B355" s="25"/>
+      <c r="B355" s="35"/>
       <c r="C355" s="25"/>
       <c r="D355" s="25"/>
       <c r="E355" s="25"/>
@@ -15184,7 +15185,7 @@
       <c r="O355" s="25"/>
     </row>
     <row r="356" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B356" s="25"/>
+      <c r="B356" s="35"/>
       <c r="C356" s="25"/>
       <c r="D356" s="25"/>
       <c r="E356" s="25"/>
@@ -15200,7 +15201,7 @@
       <c r="O356" s="25"/>
     </row>
     <row r="357" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B357" s="25"/>
+      <c r="B357" s="35"/>
       <c r="C357" s="25"/>
       <c r="D357" s="25"/>
       <c r="E357" s="25"/>
@@ -15216,7 +15217,7 @@
       <c r="O357" s="25"/>
     </row>
     <row r="358" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B358" s="25"/>
+      <c r="B358" s="35"/>
       <c r="C358" s="25"/>
       <c r="D358" s="25"/>
       <c r="E358" s="25"/>
@@ -15232,7 +15233,7 @@
       <c r="O358" s="25"/>
     </row>
     <row r="359" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B359" s="25"/>
+      <c r="B359" s="35"/>
       <c r="C359" s="25"/>
       <c r="D359" s="25"/>
       <c r="E359" s="25"/>
@@ -15248,7 +15249,7 @@
       <c r="O359" s="25"/>
     </row>
     <row r="360" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B360" s="25"/>
+      <c r="B360" s="35"/>
       <c r="C360" s="25"/>
       <c r="D360" s="25"/>
       <c r="E360" s="25"/>
@@ -15264,7 +15265,7 @@
       <c r="O360" s="25"/>
     </row>
     <row r="361" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B361" s="25"/>
+      <c r="B361" s="35"/>
       <c r="C361" s="25"/>
       <c r="D361" s="25"/>
       <c r="E361" s="25"/>
@@ -15280,7 +15281,7 @@
       <c r="O361" s="25"/>
     </row>
     <row r="362" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B362" s="25"/>
+      <c r="B362" s="35"/>
       <c r="C362" s="25"/>
       <c r="D362" s="25"/>
       <c r="E362" s="25"/>
@@ -15296,7 +15297,7 @@
       <c r="O362" s="25"/>
     </row>
     <row r="363" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B363" s="25"/>
+      <c r="B363" s="35"/>
       <c r="C363" s="25"/>
       <c r="D363" s="25"/>
       <c r="E363" s="25"/>
@@ -15312,7 +15313,7 @@
       <c r="O363" s="25"/>
     </row>
     <row r="364" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B364" s="25"/>
+      <c r="B364" s="35"/>
       <c r="C364" s="25"/>
       <c r="D364" s="25"/>
       <c r="E364" s="25"/>
@@ -15328,7 +15329,7 @@
       <c r="O364" s="25"/>
     </row>
     <row r="365" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B365" s="25"/>
+      <c r="B365" s="35"/>
       <c r="C365" s="25"/>
       <c r="D365" s="25"/>
       <c r="E365" s="25"/>
@@ -15344,7 +15345,7 @@
       <c r="O365" s="25"/>
     </row>
     <row r="366" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B366" s="25"/>
+      <c r="B366" s="35"/>
       <c r="C366" s="25"/>
       <c r="D366" s="25"/>
       <c r="E366" s="25"/>
@@ -15360,7 +15361,7 @@
       <c r="O366" s="25"/>
     </row>
     <row r="367" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B367" s="25"/>
+      <c r="B367" s="35"/>
       <c r="C367" s="25"/>
       <c r="D367" s="25"/>
       <c r="E367" s="25"/>
@@ -15376,7 +15377,7 @@
       <c r="O367" s="25"/>
     </row>
     <row r="368" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B368" s="25"/>
+      <c r="B368" s="35"/>
       <c r="C368" s="25"/>
       <c r="D368" s="25"/>
       <c r="E368" s="25"/>
@@ -15392,7 +15393,7 @@
       <c r="O368" s="25"/>
     </row>
     <row r="369" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B369" s="25"/>
+      <c r="B369" s="35"/>
       <c r="C369" s="25"/>
       <c r="D369" s="25"/>
       <c r="E369" s="25"/>
@@ -15408,7 +15409,7 @@
       <c r="O369" s="25"/>
     </row>
     <row r="370" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B370" s="25"/>
+      <c r="B370" s="35"/>
       <c r="C370" s="25"/>
       <c r="D370" s="25"/>
       <c r="E370" s="25"/>
@@ -15424,7 +15425,7 @@
       <c r="O370" s="25"/>
     </row>
     <row r="371" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B371" s="25"/>
+      <c r="B371" s="35"/>
       <c r="C371" s="25"/>
       <c r="D371" s="25"/>
       <c r="E371" s="25"/>
@@ -15440,7 +15441,7 @@
       <c r="O371" s="25"/>
     </row>
     <row r="372" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B372" s="25"/>
+      <c r="B372" s="35"/>
       <c r="C372" s="25"/>
       <c r="D372" s="25"/>
       <c r="E372" s="25"/>
@@ -15456,7 +15457,7 @@
       <c r="O372" s="25"/>
     </row>
     <row r="373" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B373" s="25"/>
+      <c r="B373" s="35"/>
       <c r="C373" s="25"/>
       <c r="D373" s="25"/>
       <c r="E373" s="25"/>
@@ -15472,7 +15473,7 @@
       <c r="O373" s="25"/>
     </row>
     <row r="374" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B374" s="25"/>
+      <c r="B374" s="35"/>
       <c r="C374" s="25"/>
       <c r="D374" s="25"/>
       <c r="E374" s="25"/>
@@ -15488,7 +15489,7 @@
       <c r="O374" s="25"/>
     </row>
     <row r="375" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B375" s="25"/>
+      <c r="B375" s="35"/>
       <c r="C375" s="25"/>
       <c r="D375" s="25"/>
       <c r="E375" s="25"/>
@@ -15504,7 +15505,7 @@
       <c r="O375" s="25"/>
     </row>
     <row r="376" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B376" s="25"/>
+      <c r="B376" s="35"/>
       <c r="C376" s="25"/>
       <c r="D376" s="25"/>
       <c r="E376" s="25"/>
@@ -15520,7 +15521,7 @@
       <c r="O376" s="25"/>
     </row>
     <row r="377" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B377" s="25"/>
+      <c r="B377" s="35"/>
       <c r="C377" s="25"/>
       <c r="D377" s="25"/>
       <c r="E377" s="25"/>
@@ -15536,7 +15537,7 @@
       <c r="O377" s="25"/>
     </row>
     <row r="378" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B378" s="25"/>
+      <c r="B378" s="35"/>
       <c r="C378" s="25"/>
       <c r="D378" s="25"/>
       <c r="E378" s="25"/>
@@ -15552,7 +15553,7 @@
       <c r="O378" s="25"/>
     </row>
     <row r="379" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B379" s="25"/>
+      <c r="B379" s="35"/>
       <c r="C379" s="25"/>
       <c r="D379" s="25"/>
       <c r="E379" s="25"/>
@@ -15568,7 +15569,7 @@
       <c r="O379" s="25"/>
     </row>
     <row r="380" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B380" s="25"/>
+      <c r="B380" s="35"/>
       <c r="C380" s="25"/>
       <c r="D380" s="25"/>
       <c r="E380" s="25"/>
@@ -15584,7 +15585,7 @@
       <c r="O380" s="25"/>
     </row>
     <row r="381" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B381" s="25"/>
+      <c r="B381" s="35"/>
       <c r="C381" s="25"/>
       <c r="D381" s="25"/>
       <c r="E381" s="25"/>
@@ -15600,7 +15601,7 @@
       <c r="O381" s="25"/>
     </row>
     <row r="382" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B382" s="25"/>
+      <c r="B382" s="35"/>
       <c r="C382" s="25"/>
       <c r="D382" s="25"/>
       <c r="E382" s="25"/>
@@ -15616,7 +15617,7 @@
       <c r="O382" s="25"/>
     </row>
     <row r="383" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B383" s="25"/>
+      <c r="B383" s="35"/>
       <c r="C383" s="25"/>
       <c r="D383" s="25"/>
       <c r="E383" s="25"/>
@@ -15632,7 +15633,7 @@
       <c r="O383" s="25"/>
     </row>
     <row r="384" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B384" s="25"/>
+      <c r="B384" s="35"/>
       <c r="C384" s="25"/>
       <c r="D384" s="25"/>
       <c r="E384" s="25"/>
@@ -15648,7 +15649,7 @@
       <c r="O384" s="25"/>
     </row>
     <row r="385" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B385" s="25"/>
+      <c r="B385" s="35"/>
       <c r="C385" s="25"/>
       <c r="D385" s="25"/>
       <c r="E385" s="25"/>
@@ -15664,7 +15665,7 @@
       <c r="O385" s="25"/>
     </row>
     <row r="386" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B386" s="25"/>
+      <c r="B386" s="35"/>
       <c r="C386" s="25"/>
       <c r="D386" s="25"/>
       <c r="E386" s="25"/>
@@ -15680,7 +15681,7 @@
       <c r="O386" s="25"/>
     </row>
     <row r="387" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B387" s="25"/>
+      <c r="B387" s="35"/>
       <c r="C387" s="25"/>
       <c r="D387" s="25"/>
       <c r="E387" s="25"/>
@@ -15696,7 +15697,7 @@
       <c r="O387" s="25"/>
     </row>
     <row r="388" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B388" s="25"/>
+      <c r="B388" s="35"/>
       <c r="C388" s="25"/>
       <c r="D388" s="25"/>
       <c r="E388" s="25"/>
@@ -15712,7 +15713,7 @@
       <c r="O388" s="25"/>
     </row>
     <row r="389" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B389" s="25"/>
+      <c r="B389" s="35"/>
       <c r="C389" s="25"/>
       <c r="D389" s="25"/>
       <c r="E389" s="25"/>
@@ -15728,7 +15729,7 @@
       <c r="O389" s="25"/>
     </row>
     <row r="390" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B390" s="25"/>
+      <c r="B390" s="35"/>
       <c r="C390" s="25"/>
       <c r="D390" s="25"/>
       <c r="E390" s="25"/>
@@ -15744,7 +15745,7 @@
       <c r="O390" s="25"/>
     </row>
     <row r="391" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B391" s="25"/>
+      <c r="B391" s="35"/>
       <c r="C391" s="25"/>
       <c r="D391" s="25"/>
       <c r="E391" s="25"/>
@@ -15760,7 +15761,7 @@
       <c r="O391" s="25"/>
     </row>
     <row r="392" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B392" s="25"/>
+      <c r="B392" s="35"/>
       <c r="C392" s="25"/>
       <c r="D392" s="25"/>
       <c r="E392" s="25"/>
@@ -15776,7 +15777,7 @@
       <c r="O392" s="25"/>
     </row>
     <row r="393" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B393" s="25"/>
+      <c r="B393" s="35"/>
       <c r="C393" s="25"/>
       <c r="D393" s="25"/>
       <c r="E393" s="25"/>
@@ -15792,7 +15793,7 @@
       <c r="O393" s="25"/>
     </row>
     <row r="394" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B394" s="25"/>
+      <c r="B394" s="35"/>
       <c r="C394" s="25"/>
       <c r="D394" s="25"/>
       <c r="E394" s="25"/>
@@ -15808,7 +15809,7 @@
       <c r="O394" s="25"/>
     </row>
     <row r="395" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B395" s="25"/>
+      <c r="B395" s="35"/>
       <c r="C395" s="25"/>
       <c r="D395" s="25"/>
       <c r="E395" s="25"/>
@@ -15824,7 +15825,7 @@
       <c r="O395" s="25"/>
     </row>
     <row r="396" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B396" s="25"/>
+      <c r="B396" s="35"/>
       <c r="C396" s="25"/>
       <c r="D396" s="25"/>
       <c r="E396" s="25"/>
@@ -15840,7 +15841,7 @@
       <c r="O396" s="25"/>
     </row>
     <row r="397" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B397" s="25"/>
+      <c r="B397" s="35"/>
       <c r="C397" s="25"/>
       <c r="D397" s="25"/>
       <c r="E397" s="25"/>
@@ -15856,7 +15857,7 @@
       <c r="O397" s="25"/>
     </row>
     <row r="398" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B398" s="25"/>
+      <c r="B398" s="35"/>
       <c r="C398" s="25"/>
       <c r="D398" s="25"/>
       <c r="E398" s="25"/>
@@ -15872,7 +15873,7 @@
       <c r="O398" s="25"/>
     </row>
     <row r="399" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B399" s="25"/>
+      <c r="B399" s="35"/>
       <c r="C399" s="25"/>
       <c r="D399" s="25"/>
       <c r="E399" s="25"/>
@@ -15888,7 +15889,7 @@
       <c r="O399" s="25"/>
     </row>
     <row r="400" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B400" s="25"/>
+      <c r="B400" s="35"/>
       <c r="C400" s="25"/>
       <c r="D400" s="25"/>
       <c r="E400" s="25"/>
@@ -15904,7 +15905,7 @@
       <c r="O400" s="25"/>
     </row>
     <row r="401" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B401" s="25"/>
+      <c r="B401" s="35"/>
       <c r="C401" s="25"/>
       <c r="D401" s="25"/>
       <c r="E401" s="25"/>
@@ -15920,7 +15921,7 @@
       <c r="O401" s="25"/>
     </row>
     <row r="402" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B402" s="25"/>
+      <c r="B402" s="35"/>
       <c r="C402" s="25"/>
       <c r="D402" s="25"/>
       <c r="E402" s="25"/>
@@ -15936,7 +15937,7 @@
       <c r="O402" s="25"/>
     </row>
     <row r="403" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B403" s="25"/>
+      <c r="B403" s="35"/>
       <c r="C403" s="25"/>
       <c r="D403" s="25"/>
       <c r="E403" s="25"/>
@@ -15952,7 +15953,7 @@
       <c r="O403" s="25"/>
     </row>
     <row r="404" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B404" s="25"/>
+      <c r="B404" s="35"/>
       <c r="C404" s="25"/>
       <c r="D404" s="25"/>
       <c r="E404" s="25"/>
@@ -15968,7 +15969,7 @@
       <c r="O404" s="25"/>
     </row>
     <row r="405" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B405" s="25"/>
+      <c r="B405" s="35"/>
       <c r="C405" s="25"/>
       <c r="D405" s="25"/>
       <c r="E405" s="25"/>
@@ -15984,7 +15985,7 @@
       <c r="O405" s="25"/>
     </row>
     <row r="406" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B406" s="25"/>
+      <c r="B406" s="35"/>
       <c r="C406" s="25"/>
       <c r="D406" s="25"/>
       <c r="E406" s="25"/>
@@ -16000,7 +16001,7 @@
       <c r="O406" s="25"/>
     </row>
     <row r="407" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B407" s="25"/>
+      <c r="B407" s="35"/>
       <c r="C407" s="25"/>
       <c r="D407" s="25"/>
       <c r="E407" s="25"/>
@@ -16016,7 +16017,7 @@
       <c r="O407" s="25"/>
     </row>
     <row r="408" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B408" s="25"/>
+      <c r="B408" s="35"/>
       <c r="C408" s="25"/>
       <c r="D408" s="25"/>
       <c r="E408" s="25"/>
@@ -16032,7 +16033,7 @@
       <c r="O408" s="25"/>
     </row>
     <row r="409" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B409" s="25"/>
+      <c r="B409" s="35"/>
       <c r="C409" s="25"/>
       <c r="D409" s="25"/>
       <c r="E409" s="25"/>
@@ -16048,7 +16049,7 @@
       <c r="O409" s="25"/>
     </row>
     <row r="410" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B410" s="25"/>
+      <c r="B410" s="35"/>
       <c r="C410" s="25"/>
       <c r="D410" s="25"/>
       <c r="E410" s="25"/>
@@ -16064,7 +16065,7 @@
       <c r="O410" s="25"/>
     </row>
     <row r="411" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B411" s="25"/>
+      <c r="B411" s="35"/>
       <c r="C411" s="25"/>
       <c r="D411" s="25"/>
       <c r="E411" s="25"/>
@@ -16080,7 +16081,7 @@
       <c r="O411" s="25"/>
     </row>
     <row r="412" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B412" s="25"/>
+      <c r="B412" s="35"/>
       <c r="C412" s="25"/>
       <c r="D412" s="25"/>
       <c r="E412" s="25"/>
@@ -16096,7 +16097,7 @@
       <c r="O412" s="25"/>
     </row>
     <row r="413" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B413" s="25"/>
+      <c r="B413" s="35"/>
       <c r="C413" s="25"/>
       <c r="D413" s="25"/>
       <c r="E413" s="25"/>
@@ -16112,7 +16113,7 @@
       <c r="O413" s="25"/>
     </row>
     <row r="414" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B414" s="25"/>
+      <c r="B414" s="35"/>
       <c r="C414" s="25"/>
       <c r="D414" s="25"/>
       <c r="E414" s="25"/>
@@ -16128,7 +16129,7 @@
       <c r="O414" s="25"/>
     </row>
     <row r="415" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B415" s="25"/>
+      <c r="B415" s="35"/>
       <c r="C415" s="25"/>
       <c r="D415" s="25"/>
       <c r="E415" s="25"/>
@@ -16144,7 +16145,7 @@
       <c r="O415" s="25"/>
     </row>
     <row r="416" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B416" s="25"/>
+      <c r="B416" s="35"/>
       <c r="C416" s="25"/>
       <c r="D416" s="25"/>
       <c r="E416" s="25"/>
@@ -16160,7 +16161,7 @@
       <c r="O416" s="25"/>
     </row>
     <row r="417" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B417" s="25"/>
+      <c r="B417" s="35"/>
       <c r="C417" s="25"/>
       <c r="D417" s="25"/>
       <c r="E417" s="25"/>
@@ -16176,7 +16177,7 @@
       <c r="O417" s="25"/>
     </row>
     <row r="418" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B418" s="25"/>
+      <c r="B418" s="35"/>
       <c r="C418" s="25"/>
       <c r="D418" s="25"/>
       <c r="E418" s="25"/>
@@ -16192,7 +16193,7 @@
       <c r="O418" s="25"/>
     </row>
     <row r="419" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B419" s="25"/>
+      <c r="B419" s="35"/>
       <c r="C419" s="25"/>
       <c r="D419" s="25"/>
       <c r="E419" s="25"/>
@@ -16208,7 +16209,7 @@
       <c r="O419" s="25"/>
     </row>
     <row r="420" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B420" s="25"/>
+      <c r="B420" s="35"/>
       <c r="C420" s="25"/>
       <c r="D420" s="25"/>
       <c r="E420" s="25"/>
@@ -16224,7 +16225,7 @@
       <c r="O420" s="25"/>
     </row>
     <row r="421" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B421" s="25"/>
+      <c r="B421" s="35"/>
       <c r="C421" s="25"/>
       <c r="D421" s="25"/>
       <c r="E421" s="25"/>
@@ -16240,7 +16241,7 @@
       <c r="O421" s="25"/>
     </row>
     <row r="422" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B422" s="25"/>
+      <c r="B422" s="35"/>
       <c r="C422" s="25"/>
       <c r="D422" s="25"/>
       <c r="E422" s="25"/>
@@ -16256,7 +16257,7 @@
       <c r="O422" s="25"/>
     </row>
     <row r="423" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B423" s="25"/>
+      <c r="B423" s="35"/>
       <c r="C423" s="25"/>
       <c r="D423" s="25"/>
       <c r="E423" s="25"/>
@@ -16272,7 +16273,7 @@
       <c r="O423" s="25"/>
     </row>
     <row r="424" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B424" s="25"/>
+      <c r="B424" s="35"/>
       <c r="C424" s="25"/>
       <c r="D424" s="25"/>
       <c r="E424" s="25"/>
@@ -16288,7 +16289,7 @@
       <c r="O424" s="25"/>
     </row>
     <row r="425" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B425" s="25"/>
+      <c r="B425" s="35"/>
       <c r="C425" s="25"/>
       <c r="D425" s="25"/>
       <c r="E425" s="25"/>
@@ -16304,7 +16305,7 @@
       <c r="O425" s="25"/>
     </row>
     <row r="426" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B426" s="25"/>
+      <c r="B426" s="35"/>
       <c r="C426" s="25"/>
       <c r="D426" s="25"/>
       <c r="E426" s="25"/>
@@ -16320,7 +16321,7 @@
       <c r="O426" s="25"/>
     </row>
     <row r="427" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B427" s="25"/>
+      <c r="B427" s="35"/>
       <c r="C427" s="25"/>
       <c r="D427" s="25"/>
       <c r="E427" s="25"/>
@@ -16336,7 +16337,7 @@
       <c r="O427" s="25"/>
     </row>
     <row r="428" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B428" s="25"/>
+      <c r="B428" s="35"/>
       <c r="C428" s="25"/>
       <c r="D428" s="25"/>
       <c r="E428" s="25"/>
@@ -16352,7 +16353,7 @@
       <c r="O428" s="25"/>
     </row>
     <row r="429" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B429" s="25"/>
+      <c r="B429" s="35"/>
       <c r="C429" s="25"/>
       <c r="D429" s="25"/>
       <c r="E429" s="25"/>
@@ -16368,7 +16369,7 @@
       <c r="O429" s="25"/>
     </row>
     <row r="430" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B430" s="25"/>
+      <c r="B430" s="35"/>
       <c r="C430" s="25"/>
       <c r="D430" s="25"/>
       <c r="E430" s="25"/>
@@ -16384,7 +16385,7 @@
       <c r="O430" s="25"/>
     </row>
     <row r="431" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B431" s="25"/>
+      <c r="B431" s="35"/>
       <c r="C431" s="25"/>
       <c r="D431" s="25"/>
       <c r="E431" s="25"/>
@@ -16400,7 +16401,7 @@
       <c r="O431" s="25"/>
     </row>
     <row r="432" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B432" s="25"/>
+      <c r="B432" s="35"/>
       <c r="C432" s="25"/>
       <c r="D432" s="25"/>
       <c r="E432" s="25"/>
@@ -16416,7 +16417,7 @@
       <c r="O432" s="25"/>
     </row>
     <row r="433" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B433" s="25"/>
+      <c r="B433" s="35"/>
       <c r="C433" s="25"/>
       <c r="D433" s="25"/>
       <c r="E433" s="25"/>
@@ -16432,7 +16433,7 @@
       <c r="O433" s="25"/>
     </row>
     <row r="434" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B434" s="25"/>
+      <c r="B434" s="35"/>
       <c r="C434" s="25"/>
       <c r="D434" s="25"/>
       <c r="E434" s="25"/>
@@ -16448,7 +16449,7 @@
       <c r="O434" s="25"/>
     </row>
     <row r="435" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B435" s="25"/>
+      <c r="B435" s="35"/>
       <c r="C435" s="25"/>
       <c r="D435" s="25"/>
       <c r="E435" s="25"/>
@@ -16464,7 +16465,7 @@
       <c r="O435" s="25"/>
     </row>
     <row r="436" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B436" s="25"/>
+      <c r="B436" s="35"/>
       <c r="C436" s="25"/>
       <c r="D436" s="25"/>
       <c r="E436" s="25"/>
@@ -16480,7 +16481,7 @@
       <c r="O436" s="25"/>
     </row>
     <row r="437" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B437" s="25"/>
+      <c r="B437" s="35"/>
       <c r="C437" s="25"/>
       <c r="D437" s="25"/>
       <c r="E437" s="25"/>
@@ -16496,7 +16497,7 @@
       <c r="O437" s="25"/>
     </row>
     <row r="438" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B438" s="25"/>
+      <c r="B438" s="35"/>
       <c r="C438" s="25"/>
       <c r="D438" s="25"/>
       <c r="E438" s="25"/>
@@ -16512,7 +16513,7 @@
       <c r="O438" s="25"/>
     </row>
     <row r="439" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B439" s="25"/>
+      <c r="B439" s="35"/>
       <c r="C439" s="25"/>
       <c r="D439" s="25"/>
       <c r="E439" s="25"/>
@@ -16528,7 +16529,7 @@
       <c r="O439" s="25"/>
     </row>
     <row r="440" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B440" s="25"/>
+      <c r="B440" s="35"/>
       <c r="C440" s="25"/>
       <c r="D440" s="25"/>
       <c r="E440" s="25"/>
@@ -16544,7 +16545,7 @@
       <c r="O440" s="25"/>
     </row>
     <row r="441" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B441" s="25"/>
+      <c r="B441" s="35"/>
       <c r="C441" s="25"/>
       <c r="D441" s="25"/>
       <c r="E441" s="25"/>
@@ -16560,7 +16561,7 @@
       <c r="O441" s="25"/>
     </row>
     <row r="442" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B442" s="25"/>
+      <c r="B442" s="35"/>
       <c r="C442" s="25"/>
       <c r="D442" s="25"/>
       <c r="E442" s="25"/>
@@ -16576,7 +16577,7 @@
       <c r="O442" s="25"/>
     </row>
     <row r="443" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B443" s="25"/>
+      <c r="B443" s="35"/>
       <c r="C443" s="25"/>
       <c r="D443" s="25"/>
       <c r="E443" s="25"/>
@@ -16592,7 +16593,7 @@
       <c r="O443" s="25"/>
     </row>
     <row r="444" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B444" s="25"/>
+      <c r="B444" s="35"/>
       <c r="C444" s="25"/>
       <c r="D444" s="25"/>
       <c r="E444" s="25"/>
@@ -16608,7 +16609,7 @@
       <c r="O444" s="25"/>
     </row>
     <row r="445" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B445" s="25"/>
+      <c r="B445" s="35"/>
       <c r="C445" s="25"/>
       <c r="D445" s="25"/>
       <c r="E445" s="25"/>
@@ -16624,7 +16625,7 @@
       <c r="O445" s="25"/>
     </row>
     <row r="446" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B446" s="25"/>
+      <c r="B446" s="35"/>
       <c r="C446" s="25"/>
       <c r="D446" s="25"/>
       <c r="E446" s="25"/>
@@ -16640,7 +16641,7 @@
       <c r="O446" s="25"/>
     </row>
     <row r="447" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B447" s="25"/>
+      <c r="B447" s="35"/>
       <c r="C447" s="25"/>
       <c r="D447" s="25"/>
       <c r="E447" s="25"/>
@@ -16656,7 +16657,7 @@
       <c r="O447" s="25"/>
     </row>
     <row r="448" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B448" s="25"/>
+      <c r="B448" s="35"/>
       <c r="C448" s="25"/>
       <c r="D448" s="25"/>
       <c r="E448" s="25"/>
@@ -16672,7 +16673,7 @@
       <c r="O448" s="25"/>
     </row>
     <row r="449" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B449" s="25"/>
+      <c r="B449" s="35"/>
       <c r="C449" s="25"/>
       <c r="D449" s="25"/>
       <c r="E449" s="25"/>
@@ -16688,7 +16689,7 @@
       <c r="O449" s="25"/>
     </row>
     <row r="450" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B450" s="25"/>
+      <c r="B450" s="35"/>
       <c r="C450" s="25"/>
       <c r="D450" s="25"/>
       <c r="E450" s="25"/>
@@ -16704,7 +16705,7 @@
       <c r="O450" s="25"/>
     </row>
     <row r="451" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B451" s="25"/>
+      <c r="B451" s="35"/>
       <c r="C451" s="25"/>
       <c r="D451" s="25"/>
       <c r="E451" s="25"/>
@@ -16720,7 +16721,7 @@
       <c r="O451" s="25"/>
     </row>
     <row r="452" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B452" s="25"/>
+      <c r="B452" s="35"/>
       <c r="C452" s="25"/>
       <c r="D452" s="25"/>
       <c r="E452" s="25"/>
@@ -16736,7 +16737,7 @@
       <c r="O452" s="25"/>
     </row>
     <row r="453" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B453" s="25"/>
+      <c r="B453" s="35"/>
       <c r="C453" s="25"/>
       <c r="D453" s="25"/>
       <c r="E453" s="25"/>
@@ -16752,7 +16753,7 @@
       <c r="O453" s="25"/>
     </row>
     <row r="454" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B454" s="25"/>
+      <c r="B454" s="35"/>
       <c r="C454" s="25"/>
       <c r="D454" s="25"/>
       <c r="E454" s="25"/>
@@ -16768,7 +16769,7 @@
       <c r="O454" s="25"/>
     </row>
     <row r="455" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B455" s="25"/>
+      <c r="B455" s="35"/>
       <c r="C455" s="25"/>
       <c r="D455" s="25"/>
       <c r="E455" s="25"/>
@@ -16784,7 +16785,7 @@
       <c r="O455" s="25"/>
     </row>
     <row r="456" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B456" s="25"/>
+      <c r="B456" s="35"/>
       <c r="C456" s="25"/>
       <c r="D456" s="25"/>
       <c r="E456" s="25"/>
@@ -16800,7 +16801,7 @@
       <c r="O456" s="25"/>
     </row>
     <row r="457" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B457" s="25"/>
+      <c r="B457" s="35"/>
       <c r="C457" s="25"/>
       <c r="D457" s="25"/>
       <c r="E457" s="25"/>
@@ -16816,7 +16817,7 @@
       <c r="O457" s="25"/>
     </row>
     <row r="458" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B458" s="25"/>
+      <c r="B458" s="35"/>
       <c r="C458" s="25"/>
       <c r="D458" s="25"/>
       <c r="E458" s="25"/>
@@ -16832,7 +16833,7 @@
       <c r="O458" s="25"/>
     </row>
     <row r="459" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B459" s="25"/>
+      <c r="B459" s="35"/>
       <c r="C459" s="25"/>
       <c r="D459" s="25"/>
       <c r="E459" s="25"/>
@@ -16848,7 +16849,7 @@
       <c r="O459" s="25"/>
     </row>
     <row r="460" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B460" s="25"/>
+      <c r="B460" s="35"/>
       <c r="C460" s="25"/>
       <c r="D460" s="25"/>
       <c r="E460" s="25"/>
@@ -16864,7 +16865,7 @@
       <c r="O460" s="25"/>
     </row>
     <row r="461" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B461" s="25"/>
+      <c r="B461" s="35"/>
       <c r="C461" s="25"/>
       <c r="D461" s="25"/>
       <c r="E461" s="25"/>
@@ -16880,7 +16881,7 @@
       <c r="O461" s="25"/>
     </row>
     <row r="462" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B462" s="25"/>
+      <c r="B462" s="35"/>
       <c r="C462" s="25"/>
       <c r="D462" s="25"/>
       <c r="E462" s="25"/>
@@ -16896,7 +16897,7 @@
       <c r="O462" s="25"/>
     </row>
     <row r="463" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B463" s="25"/>
+      <c r="B463" s="35"/>
       <c r="C463" s="25"/>
       <c r="D463" s="25"/>
       <c r="E463" s="25"/>
@@ -16912,7 +16913,7 @@
       <c r="O463" s="25"/>
     </row>
     <row r="464" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B464" s="25"/>
+      <c r="B464" s="35"/>
       <c r="C464" s="25"/>
       <c r="D464" s="25"/>
       <c r="E464" s="25"/>
@@ -16928,7 +16929,7 @@
       <c r="O464" s="25"/>
     </row>
     <row r="465" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B465" s="25"/>
+      <c r="B465" s="35"/>
       <c r="C465" s="25"/>
       <c r="D465" s="25"/>
       <c r="E465" s="25"/>
@@ -16944,7 +16945,7 @@
       <c r="O465" s="25"/>
     </row>
     <row r="466" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B466" s="25"/>
+      <c r="B466" s="35"/>
       <c r="C466" s="25"/>
       <c r="D466" s="25"/>
       <c r="E466" s="25"/>
@@ -16960,7 +16961,7 @@
       <c r="O466" s="25"/>
     </row>
     <row r="467" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B467" s="25"/>
+      <c r="B467" s="35"/>
       <c r="C467" s="25"/>
       <c r="D467" s="25"/>
       <c r="E467" s="25"/>
@@ -16976,7 +16977,7 @@
       <c r="O467" s="25"/>
     </row>
     <row r="468" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B468" s="25"/>
+      <c r="B468" s="35"/>
       <c r="C468" s="25"/>
       <c r="D468" s="25"/>
       <c r="E468" s="25"/>
@@ -16992,7 +16993,7 @@
       <c r="O468" s="25"/>
     </row>
     <row r="469" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B469" s="25"/>
+      <c r="B469" s="35"/>
       <c r="C469" s="25"/>
       <c r="D469" s="25"/>
       <c r="E469" s="25"/>
@@ -17008,7 +17009,7 @@
       <c r="O469" s="25"/>
     </row>
     <row r="470" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B470" s="25"/>
+      <c r="B470" s="35"/>
       <c r="C470" s="25"/>
       <c r="D470" s="25"/>
       <c r="E470" s="25"/>
@@ -17024,7 +17025,7 @@
       <c r="O470" s="25"/>
     </row>
     <row r="471" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B471" s="25"/>
+      <c r="B471" s="35"/>
       <c r="C471" s="25"/>
       <c r="D471" s="25"/>
       <c r="E471" s="25"/>
@@ -17040,7 +17041,7 @@
       <c r="O471" s="25"/>
     </row>
     <row r="472" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B472" s="25"/>
+      <c r="B472" s="35"/>
       <c r="C472" s="25"/>
       <c r="D472" s="25"/>
       <c r="E472" s="25"/>
@@ -17056,7 +17057,7 @@
       <c r="O472" s="25"/>
     </row>
     <row r="473" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B473" s="25"/>
+      <c r="B473" s="35"/>
       <c r="C473" s="25"/>
       <c r="D473" s="25"/>
       <c r="E473" s="25"/>
@@ -17072,7 +17073,7 @@
       <c r="O473" s="25"/>
     </row>
     <row r="474" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B474" s="25"/>
+      <c r="B474" s="35"/>
       <c r="C474" s="25"/>
       <c r="D474" s="25"/>
       <c r="E474" s="25"/>
@@ -17088,7 +17089,7 @@
       <c r="O474" s="25"/>
     </row>
     <row r="475" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B475" s="25"/>
+      <c r="B475" s="35"/>
       <c r="C475" s="25"/>
       <c r="D475" s="25"/>
       <c r="E475" s="25"/>
@@ -17104,7 +17105,7 @@
       <c r="O475" s="25"/>
     </row>
     <row r="476" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B476" s="25"/>
+      <c r="B476" s="35"/>
       <c r="C476" s="25"/>
       <c r="D476" s="25"/>
       <c r="E476" s="25"/>
@@ -17120,7 +17121,7 @@
       <c r="O476" s="25"/>
     </row>
     <row r="477" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B477" s="25"/>
+      <c r="B477" s="35"/>
       <c r="C477" s="25"/>
       <c r="D477" s="25"/>
       <c r="E477" s="25"/>
@@ -17136,7 +17137,7 @@
       <c r="O477" s="25"/>
     </row>
     <row r="478" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B478" s="25"/>
+      <c r="B478" s="35"/>
       <c r="C478" s="25"/>
       <c r="D478" s="25"/>
       <c r="E478" s="25"/>
@@ -17152,7 +17153,7 @@
       <c r="O478" s="25"/>
     </row>
     <row r="479" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B479" s="25"/>
+      <c r="B479" s="35"/>
       <c r="C479" s="25"/>
       <c r="D479" s="25"/>
       <c r="E479" s="25"/>
@@ -17168,7 +17169,7 @@
       <c r="O479" s="25"/>
     </row>
     <row r="480" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B480" s="25"/>
+      <c r="B480" s="35"/>
       <c r="C480" s="25"/>
       <c r="D480" s="25"/>
       <c r="E480" s="25"/>
@@ -17184,7 +17185,7 @@
       <c r="O480" s="25"/>
     </row>
     <row r="481" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B481" s="25"/>
+      <c r="B481" s="35"/>
       <c r="C481" s="25"/>
       <c r="D481" s="25"/>
       <c r="E481" s="25"/>
@@ -17200,7 +17201,7 @@
       <c r="O481" s="25"/>
     </row>
     <row r="482" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B482" s="25"/>
+      <c r="B482" s="35"/>
       <c r="C482" s="25"/>
       <c r="D482" s="25"/>
       <c r="E482" s="25"/>
@@ -17216,7 +17217,7 @@
       <c r="O482" s="25"/>
     </row>
     <row r="483" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B483" s="25"/>
+      <c r="B483" s="35"/>
       <c r="C483" s="25"/>
       <c r="D483" s="25"/>
       <c r="E483" s="25"/>
@@ -17232,7 +17233,7 @@
       <c r="O483" s="25"/>
     </row>
     <row r="484" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B484" s="25"/>
+      <c r="B484" s="35"/>
       <c r="C484" s="25"/>
       <c r="D484" s="25"/>
       <c r="E484" s="25"/>
@@ -17248,7 +17249,7 @@
       <c r="O484" s="25"/>
     </row>
     <row r="485" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B485" s="25"/>
+      <c r="B485" s="35"/>
       <c r="C485" s="25"/>
       <c r="D485" s="25"/>
       <c r="E485" s="25"/>
@@ -17264,7 +17265,7 @@
       <c r="O485" s="25"/>
     </row>
     <row r="486" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B486" s="25"/>
+      <c r="B486" s="35"/>
       <c r="C486" s="25"/>
       <c r="D486" s="25"/>
       <c r="E486" s="25"/>
@@ -17280,7 +17281,7 @@
       <c r="O486" s="25"/>
     </row>
     <row r="487" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B487" s="25"/>
+      <c r="B487" s="35"/>
       <c r="C487" s="25"/>
       <c r="D487" s="25"/>
       <c r="E487" s="25"/>
@@ -17296,7 +17297,7 @@
       <c r="O487" s="25"/>
     </row>
     <row r="488" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B488" s="25"/>
+      <c r="B488" s="35"/>
       <c r="C488" s="25"/>
       <c r="D488" s="25"/>
       <c r="E488" s="25"/>
@@ -17312,7 +17313,7 @@
       <c r="O488" s="25"/>
     </row>
     <row r="489" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B489" s="25"/>
+      <c r="B489" s="35"/>
       <c r="C489" s="25"/>
       <c r="D489" s="25"/>
       <c r="E489" s="25"/>
@@ -17328,7 +17329,7 @@
       <c r="O489" s="25"/>
     </row>
     <row r="490" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B490" s="25"/>
+      <c r="B490" s="35"/>
       <c r="C490" s="25"/>
       <c r="D490" s="25"/>
       <c r="E490" s="25"/>
@@ -17344,7 +17345,7 @@
       <c r="O490" s="25"/>
     </row>
     <row r="491" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B491" s="25"/>
+      <c r="B491" s="35"/>
       <c r="C491" s="25"/>
       <c r="D491" s="25"/>
       <c r="E491" s="25"/>
@@ -17360,7 +17361,7 @@
       <c r="O491" s="25"/>
     </row>
     <row r="492" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B492" s="25"/>
+      <c r="B492" s="35"/>
       <c r="C492" s="25"/>
       <c r="D492" s="25"/>
       <c r="E492" s="25"/>
@@ -17376,7 +17377,7 @@
       <c r="O492" s="25"/>
     </row>
     <row r="493" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B493" s="25"/>
+      <c r="B493" s="35"/>
       <c r="C493" s="25"/>
       <c r="D493" s="25"/>
       <c r="E493" s="25"/>
@@ -17392,7 +17393,7 @@
       <c r="O493" s="25"/>
     </row>
     <row r="494" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B494" s="25"/>
+      <c r="B494" s="35"/>
       <c r="C494" s="25"/>
       <c r="D494" s="25"/>
       <c r="E494" s="25"/>
@@ -17408,7 +17409,7 @@
       <c r="O494" s="25"/>
     </row>
     <row r="495" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B495" s="25"/>
+      <c r="B495" s="35"/>
       <c r="C495" s="25"/>
       <c r="D495" s="25"/>
       <c r="E495" s="25"/>
@@ -17424,7 +17425,7 @@
       <c r="O495" s="25"/>
     </row>
     <row r="496" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B496" s="25"/>
+      <c r="B496" s="35"/>
       <c r="C496" s="25"/>
       <c r="D496" s="25"/>
       <c r="E496" s="25"/>
@@ -17440,7 +17441,7 @@
       <c r="O496" s="25"/>
     </row>
     <row r="497" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B497" s="25"/>
+      <c r="B497" s="35"/>
       <c r="C497" s="25"/>
       <c r="D497" s="25"/>
       <c r="E497" s="25"/>
@@ -17456,7 +17457,7 @@
       <c r="O497" s="25"/>
     </row>
     <row r="498" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B498" s="25"/>
+      <c r="B498" s="35"/>
       <c r="C498" s="25"/>
       <c r="D498" s="25"/>
       <c r="E498" s="25"/>
@@ -17472,7 +17473,7 @@
       <c r="O498" s="25"/>
     </row>
     <row r="499" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B499" s="25"/>
+      <c r="B499" s="35"/>
       <c r="C499" s="25"/>
       <c r="D499" s="25"/>
       <c r="E499" s="25"/>
@@ -17488,7 +17489,7 @@
       <c r="O499" s="25"/>
     </row>
     <row r="500" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B500" s="25"/>
+      <c r="B500" s="35"/>
       <c r="C500" s="25"/>
       <c r="D500" s="25"/>
       <c r="E500" s="25"/>
@@ -17505,5 +17506,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/FreeLayout/Mau_Report_Detail.xlsx
+++ b/FreeLayout/Mau_Report_Detail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SCM Inovation2\SCM_Inovation\FreeLayout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED83B791-3F6E-4C02-BA43-A39AE9A9D9F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F35C49-D49F-4E13-91DD-1785A6D701E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-810" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2A4EDF3B-70CC-4D79-8378-AD958291D9C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2A4EDF3B-70CC-4D79-8378-AD958291D9C4}"/>
   </bookViews>
   <sheets>
     <sheet name="Report details" sheetId="1" r:id="rId1"/>
@@ -9477,10 +9477,19 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="46"/>
+      <c r="H1" s="46">
+        <f>SUBTOTAL(9,H3:H1000)</f>
+        <v>0</v>
+      </c>
       <c r="I1" s="6"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
+      <c r="J1" s="47">
+        <f>SUBTOTAL(9,J3:J1000)</f>
+        <v>0</v>
+      </c>
+      <c r="K1" s="47">
+        <f>SUBTOTAL(9,K3:K1000)</f>
+        <v>0</v>
+      </c>
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
